--- a/paper/sensitivity_analysis_all.xlsx
+++ b/paper/sensitivity_analysis_all.xlsx
@@ -502,10 +502,10 @@
         <v>0.66462</v>
       </c>
       <c r="I2" t="n">
-        <v>0.22974</v>
+        <v>0.2318</v>
       </c>
       <c r="J2" t="n">
-        <v>0.62624</v>
+        <v>0.6249600000000002</v>
       </c>
     </row>
     <row r="3">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.27042</v>
+        <v>0.2724799999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.28974</v>
+        <v>0.29076</v>
       </c>
       <c r="G3" t="n">
-        <v>0.48</v>
+        <v>0.47386</v>
       </c>
       <c r="H3" t="n">
-        <v>0.76922</v>
+        <v>0.7651199999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.22974</v>
+        <v>0.2318</v>
       </c>
       <c r="J3" t="n">
-        <v>0.62624</v>
+        <v>0.6249600000000002</v>
       </c>
     </row>
     <row r="4">
@@ -570,22 +570,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.89666</v>
+        <v>0.8974400000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9107799999999999</v>
+        <v>0.9113599999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>0.91616</v>
+        <v>0.9173</v>
       </c>
       <c r="H4" t="n">
         <v>0.9812799999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.22974</v>
+        <v>0.2318</v>
       </c>
       <c r="J4" t="n">
-        <v>0.62624</v>
+        <v>0.6249600000000002</v>
       </c>
     </row>
     <row r="5">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.08033999999999999</v>
+        <v>0.08102000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08874</v>
+        <v>0.08972000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3672</v>
+        <v>0.36924</v>
       </c>
       <c r="H5" t="n">
-        <v>0.70564</v>
+        <v>0.7056600000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.227</v>
+        <v>0.22704</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5823</v>
+        <v>0.5847</v>
       </c>
     </row>
     <row r="6">
@@ -650,22 +650,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.3073399999999999</v>
+        <v>0.30806</v>
       </c>
       <c r="F6" t="n">
-        <v>0.33024</v>
+        <v>0.32668</v>
       </c>
       <c r="G6" t="n">
-        <v>0.50668</v>
+        <v>0.5005000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7918000000000001</v>
+        <v>0.7866799999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.227</v>
+        <v>0.22704</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5823</v>
+        <v>0.5847</v>
       </c>
     </row>
     <row r="7">
@@ -690,22 +690,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.88964</v>
+        <v>0.89276</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9061</v>
+        <v>0.90848</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9020999999999999</v>
+        <v>0.90564</v>
       </c>
       <c r="H7" t="n">
         <v>0.98712</v>
       </c>
       <c r="I7" t="n">
-        <v>0.227</v>
+        <v>0.22704</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5823</v>
+        <v>0.5847</v>
       </c>
     </row>
     <row r="8">
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.05026000000000001</v>
+        <v>0.0523</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04973999999999999</v>
+        <v>0.0518</v>
       </c>
       <c r="G8" t="n">
         <v>0.34052</v>
@@ -742,10 +742,10 @@
         <v>0.68102</v>
       </c>
       <c r="I8" t="n">
-        <v>0.20242</v>
+        <v>0.22084</v>
       </c>
       <c r="J8" t="n">
-        <v>0.63628</v>
+        <v>0.61894</v>
       </c>
     </row>
     <row r="9">
@@ -770,22 +770,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.25268</v>
+        <v>0.27314</v>
       </c>
       <c r="F9" t="n">
-        <v>0.26924</v>
+        <v>0.2882000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>0.47078</v>
+        <v>0.48206</v>
       </c>
       <c r="H9" t="n">
         <v>0.77128</v>
       </c>
       <c r="I9" t="n">
-        <v>0.20242</v>
+        <v>0.22084</v>
       </c>
       <c r="J9" t="n">
-        <v>0.63628</v>
+        <v>0.61894</v>
       </c>
     </row>
     <row r="10">
@@ -810,22 +810,22 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.88896</v>
+        <v>0.89208</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9050800000000001</v>
+        <v>0.9068400000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>0.91964</v>
+        <v>0.92548</v>
       </c>
       <c r="H10" t="n">
         <v>0.9941600000000002</v>
       </c>
       <c r="I10" t="n">
-        <v>0.20242</v>
+        <v>0.22084</v>
       </c>
       <c r="J10" t="n">
-        <v>0.63628</v>
+        <v>0.61894</v>
       </c>
     </row>
     <row r="11">
@@ -850,22 +850,22 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.05366</v>
+        <v>0.05776</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0554</v>
+        <v>0.06052</v>
       </c>
       <c r="G11" t="n">
-        <v>0.34768</v>
+        <v>0.3497400000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6799999999999999</v>
+        <v>0.6800200000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.24686</v>
+        <v>0.23796</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5992</v>
+        <v>0.6024799999999999</v>
       </c>
     </row>
     <row r="12">
@@ -890,22 +890,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.30052</v>
+        <v>0.29572</v>
       </c>
       <c r="F12" t="n">
-        <v>0.32</v>
+        <v>0.31282</v>
       </c>
       <c r="G12" t="n">
-        <v>0.50154</v>
+        <v>0.49128</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7784799999999998</v>
+        <v>0.7733399999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.24686</v>
+        <v>0.23796</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5992</v>
+        <v>0.6024799999999999</v>
       </c>
     </row>
     <row r="13">
@@ -930,22 +930,22 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.89972</v>
+        <v>0.8981999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>0.91838</v>
+        <v>0.9149200000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>0.90798</v>
+        <v>0.91152</v>
       </c>
       <c r="H13" t="n">
         <v>0.98712</v>
       </c>
       <c r="I13" t="n">
-        <v>0.24686</v>
+        <v>0.23796</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5992</v>
+        <v>0.6024799999999999</v>
       </c>
     </row>
     <row r="14">
@@ -982,10 +982,10 @@
         <v>0.6881999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1975999999999999</v>
+        <v>0.21404</v>
       </c>
       <c r="J14" t="n">
-        <v>0.64516</v>
+        <v>0.6303000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1010,22 +1010,22 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.25468</v>
+        <v>0.27112</v>
       </c>
       <c r="F15" t="n">
-        <v>0.27076</v>
+        <v>0.28768</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4656399999999999</v>
+        <v>0.47898</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7702800000000001</v>
+        <v>0.7712800000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1975999999999999</v>
+        <v>0.21404</v>
       </c>
       <c r="J15" t="n">
-        <v>0.64516</v>
+        <v>0.6303000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1050,22 +1050,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.89984</v>
+        <v>0.9014200000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9156000000000001</v>
+        <v>0.91676</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9243399999999999</v>
+        <v>0.9267</v>
       </c>
       <c r="H16" t="n">
         <v>0.9941600000000002</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1975999999999999</v>
+        <v>0.21404</v>
       </c>
       <c r="J16" t="n">
-        <v>0.64516</v>
+        <v>0.6303000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1090,22 +1090,22 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.04820000000000001</v>
+        <v>0.05300000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>0.04564</v>
+        <v>0.05078000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3333199999999999</v>
+        <v>0.3364200000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>0.68102</v>
+        <v>0.68408</v>
       </c>
       <c r="I17" t="n">
-        <v>0.22428</v>
+        <v>0.2365800000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6266</v>
+        <v>0.6118199999999999</v>
       </c>
     </row>
     <row r="18">
@@ -1130,22 +1130,22 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.27248</v>
+        <v>0.2895800000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2892400000000001</v>
+        <v>0.30206</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4759</v>
+        <v>0.4830599999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7764</v>
+        <v>0.7743599999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.22428</v>
+        <v>0.2365800000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6266</v>
+        <v>0.6118199999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1170,22 +1170,22 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.89908</v>
+        <v>0.9014</v>
       </c>
       <c r="F19" t="n">
-        <v>0.91088</v>
+        <v>0.9114800000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>0.92778</v>
+        <v>0.9312800000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9907</v>
+        <v>0.9883200000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>0.22428</v>
+        <v>0.2365800000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6266</v>
+        <v>0.6118199999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1210,22 +1210,22 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.06804</v>
+        <v>0.06874</v>
       </c>
       <c r="F20" t="n">
-        <v>0.07382</v>
+        <v>0.07486</v>
       </c>
       <c r="G20" t="n">
-        <v>0.36</v>
+        <v>0.36206</v>
       </c>
       <c r="H20" t="n">
-        <v>0.69336</v>
+        <v>0.6933400000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>0.23726</v>
+        <v>0.23314</v>
       </c>
       <c r="J20" t="n">
-        <v>0.58042</v>
+        <v>0.5869399999999999</v>
       </c>
     </row>
     <row r="21">
@@ -1250,22 +1250,22 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.3053</v>
+        <v>0.30188</v>
       </c>
       <c r="F21" t="n">
-        <v>0.32052</v>
+        <v>0.31438</v>
       </c>
       <c r="G21" t="n">
-        <v>0.50258</v>
+        <v>0.4902800000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>0.77742</v>
+        <v>0.7723199999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.23726</v>
+        <v>0.23314</v>
       </c>
       <c r="J21" t="n">
-        <v>0.58042</v>
+        <v>0.5869399999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1290,22 +1290,22 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.8857200000000001</v>
+        <v>0.8888199999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>0.90084</v>
+        <v>0.9032</v>
       </c>
       <c r="G22" t="n">
-        <v>0.90784</v>
+        <v>0.91138</v>
       </c>
       <c r="H22" t="n">
         <v>0.98248</v>
       </c>
       <c r="I22" t="n">
-        <v>0.23726</v>
+        <v>0.23314</v>
       </c>
       <c r="J22" t="n">
-        <v>0.58042</v>
+        <v>0.5869399999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1330,10 +1330,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.04754</v>
+        <v>0.04958000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>0.04974</v>
+        <v>0.0518</v>
       </c>
       <c r="G23" t="n">
         <v>0.34358</v>
@@ -1342,10 +1342,10 @@
         <v>0.6851199999999998</v>
       </c>
       <c r="I23" t="n">
-        <v>0.20444</v>
+        <v>0.2112999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6471399999999999</v>
+        <v>0.63826</v>
       </c>
     </row>
     <row r="24">
@@ -1370,22 +1370,22 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.25198</v>
+        <v>0.2608799999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>0.26614</v>
+        <v>0.27386</v>
       </c>
       <c r="G24" t="n">
-        <v>0.46256</v>
+        <v>0.4718000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>0.76306</v>
+        <v>0.7579199999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>0.20444</v>
+        <v>0.2112999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6471399999999999</v>
+        <v>0.63826</v>
       </c>
     </row>
     <row r="25">
@@ -1410,22 +1410,22 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.8991199999999999</v>
+        <v>0.8991400000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>0.91792</v>
+        <v>0.9197200000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>0.92322</v>
+        <v>0.91974</v>
       </c>
       <c r="H25" t="n">
         <v>0.9941600000000002</v>
       </c>
       <c r="I25" t="n">
-        <v>0.20444</v>
+        <v>0.2112999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6471399999999999</v>
+        <v>0.63826</v>
       </c>
     </row>
     <row r="26">
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.05574000000000001</v>
+        <v>0.05914000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>0.05848</v>
+        <v>0.06258</v>
       </c>
       <c r="G26" t="n">
         <v>0.34666</v>
@@ -1462,10 +1462,10 @@
         <v>0.68308</v>
       </c>
       <c r="I26" t="n">
-        <v>0.25776</v>
+        <v>0.24138</v>
       </c>
       <c r="J26" t="n">
-        <v>0.5970399999999999</v>
+        <v>0.6061399999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1490,22 +1490,22 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.3135</v>
+        <v>0.30052</v>
       </c>
       <c r="F27" t="n">
-        <v>0.33334</v>
+        <v>0.31998</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5158800000000001</v>
+        <v>0.49436</v>
       </c>
       <c r="H27" t="n">
-        <v>0.7795</v>
+        <v>0.7743599999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>0.25776</v>
+        <v>0.24138</v>
       </c>
       <c r="J27" t="n">
-        <v>0.5970399999999999</v>
+        <v>0.6061399999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.9105399999999999</v>
+        <v>0.9066599999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>0.92644</v>
+        <v>0.9212199999999999</v>
       </c>
       <c r="G28" t="n">
         <v>0.9206999999999999</v>
@@ -1542,10 +1542,10 @@
         <v>0.98712</v>
       </c>
       <c r="I28" t="n">
-        <v>0.25776</v>
+        <v>0.24138</v>
       </c>
       <c r="J28" t="n">
-        <v>0.5970399999999999</v>
+        <v>0.6061399999999999</v>
       </c>
     </row>
     <row r="29">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.07896</v>
+        <v>0.08102000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>0.08819999999999999</v>
+        <v>0.09024</v>
       </c>
       <c r="G29" t="n">
         <v>0.37744</v>
@@ -1582,10 +1582,10 @@
         <v>0.7066800000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>0.20174</v>
+        <v>0.18598</v>
       </c>
       <c r="J29" t="n">
-        <v>0.6105400000000001</v>
+        <v>0.61028</v>
       </c>
     </row>
     <row r="30">
@@ -1610,22 +1610,22 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.2807</v>
+        <v>0.267</v>
       </c>
       <c r="F30" t="n">
-        <v>0.29436</v>
+        <v>0.2769200000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>0.49436</v>
+        <v>0.4851</v>
       </c>
       <c r="H30" t="n">
-        <v>0.77642</v>
+        <v>0.7640999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>0.20174</v>
+        <v>0.18598</v>
       </c>
       <c r="J30" t="n">
-        <v>0.6105400000000001</v>
+        <v>0.61028</v>
       </c>
     </row>
     <row r="31">
@@ -1650,22 +1650,22 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.89124</v>
+        <v>0.8772800000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>0.91028</v>
+        <v>0.89976</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9348000000000001</v>
+        <v>0.92666</v>
       </c>
       <c r="H31" t="n">
         <v>0.9836599999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>0.20174</v>
+        <v>0.18598</v>
       </c>
       <c r="J31" t="n">
-        <v>0.6105400000000001</v>
+        <v>0.61028</v>
       </c>
     </row>
     <row r="32">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.194172, "environmental": 0.131673, "comfort": 0.401912, "practicality": 0.272243}</t>
+          <t>{"energy_cost": 0.1943, "environmental": 0.131354, "comfort": 0.403745, "practicality": 0.2706}</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1702,10 +1702,10 @@
         <v>0.77434</v>
       </c>
       <c r="I32" t="n">
-        <v>0.09777999999999998</v>
+        <v>0.09576000000000001</v>
       </c>
       <c r="J32" t="n">
-        <v>0.59806</v>
+        <v>0.62416</v>
       </c>
     </row>
     <row r="33">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.194172, "environmental": 0.131673, "comfort": 0.401912, "practicality": 0.272243}</t>
+          <t>{"energy_cost": 0.1943, "environmental": 0.131354, "comfort": 0.403745, "practicality": 0.2706}</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1730,22 +1730,22 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.33128</v>
+        <v>0.32926</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3527999999999999</v>
+        <v>0.35026</v>
       </c>
       <c r="G33" t="n">
-        <v>0.53538</v>
+        <v>0.5394599999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8</v>
+        <v>0.79588</v>
       </c>
       <c r="I33" t="n">
-        <v>0.09777999999999998</v>
+        <v>0.09576000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>0.59806</v>
+        <v>0.62416</v>
       </c>
     </row>
     <row r="34">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.194172, "environmental": 0.131673, "comfort": 0.401912, "practicality": 0.272243}</t>
+          <t>{"energy_cost": 0.1943, "environmental": 0.131354, "comfort": 0.403745, "practicality": 0.2706}</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1770,22 +1770,22 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9293400000000001</v>
+        <v>0.95342</v>
       </c>
       <c r="F34" t="n">
-        <v>0.94702</v>
+        <v>0.96508</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9091800000000001</v>
+        <v>0.9406399999999999</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>0.09777999999999998</v>
+        <v>0.09576000000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>0.59806</v>
+        <v>0.62416</v>
       </c>
     </row>
     <row r="35">
@@ -1822,10 +1822,10 @@
         <v>0.79078</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1661799999999999</v>
+        <v>0.15246</v>
       </c>
       <c r="J35" t="n">
-        <v>0.5196999999999999</v>
+        <v>0.5489599999999999</v>
       </c>
     </row>
     <row r="36">
@@ -1850,22 +1850,22 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.4407</v>
+        <v>0.42698</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4646199999999999</v>
+        <v>0.44924</v>
       </c>
       <c r="G36" t="n">
-        <v>0.61026</v>
+        <v>0.61128</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8359</v>
+        <v>0.8256399999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1661799999999999</v>
+        <v>0.15246</v>
       </c>
       <c r="J36" t="n">
-        <v>0.5196999999999999</v>
+        <v>0.5489599999999999</v>
       </c>
     </row>
     <row r="37">
@@ -1890,22 +1890,22 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.9603999999999999</v>
+        <v>0.9759399999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>0.97028</v>
+        <v>0.9819799999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9464399999999999</v>
+        <v>0.9686</v>
       </c>
       <c r="H37" t="n">
         <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1661799999999999</v>
+        <v>0.15246</v>
       </c>
       <c r="J37" t="n">
-        <v>0.5196999999999999</v>
+        <v>0.5489599999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1942,10 +1942,10 @@
         <v>0.7640999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>0.07999999999999999</v>
+        <v>0.08068</v>
       </c>
       <c r="J38" t="n">
-        <v>0.6575</v>
+        <v>0.67626</v>
       </c>
     </row>
     <row r="39">
@@ -1970,22 +1970,22 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.2711</v>
+        <v>0.27178</v>
       </c>
       <c r="F39" t="n">
-        <v>0.28566</v>
+        <v>0.28664</v>
       </c>
       <c r="G39" t="n">
-        <v>0.48206</v>
+        <v>0.48308</v>
       </c>
       <c r="H39" t="n">
-        <v>0.7835799999999999</v>
+        <v>0.77744</v>
       </c>
       <c r="I39" t="n">
-        <v>0.07999999999999999</v>
+        <v>0.08068</v>
       </c>
       <c r="J39" t="n">
-        <v>0.6575</v>
+        <v>0.67626</v>
       </c>
     </row>
     <row r="40">
@@ -2010,22 +2010,22 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.9286</v>
+        <v>0.94804</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9458800000000001</v>
+        <v>0.961</v>
       </c>
       <c r="G40" t="n">
-        <v>0.92552</v>
+        <v>0.9313399999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>0.99886</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>0.07999999999999999</v>
+        <v>0.08068</v>
       </c>
       <c r="J40" t="n">
-        <v>0.6575</v>
+        <v>0.67626</v>
       </c>
     </row>
     <row r="41">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}</t>
+          <t>{"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2050,22 +2050,22 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.07146</v>
+        <v>0.07076</v>
       </c>
       <c r="F41" t="n">
         <v>0.08</v>
       </c>
       <c r="G41" t="n">
-        <v>0.37436</v>
+        <v>0.37538</v>
       </c>
       <c r="H41" t="n">
-        <v>0.69948</v>
+        <v>0.6974400000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1935</v>
+        <v>0.1798400000000001</v>
       </c>
       <c r="J41" t="n">
-        <v>0.6169600000000001</v>
+        <v>0.6227799999999998</v>
       </c>
     </row>
     <row r="42">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}</t>
+          <t>{"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2090,22 +2090,22 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.26496</v>
+        <v>0.2506</v>
       </c>
       <c r="F42" t="n">
-        <v>0.2795</v>
+        <v>0.2646</v>
       </c>
       <c r="G42" t="n">
-        <v>0.48102</v>
+        <v>0.4800000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>0.76922</v>
+        <v>0.75898</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1935</v>
+        <v>0.1798400000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>0.6169600000000001</v>
+        <v>0.6227799999999998</v>
       </c>
     </row>
     <row r="43">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}</t>
+          <t>{"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2130,22 +2130,22 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.88192</v>
+        <v>0.8733799999999998</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9026799999999999</v>
+        <v>0.89628</v>
       </c>
       <c r="G43" t="n">
-        <v>0.9196</v>
+        <v>0.9137999999999999</v>
       </c>
       <c r="H43" t="n">
         <v>0.9836599999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1935</v>
+        <v>0.1798400000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>0.6169600000000001</v>
+        <v>0.6227799999999998</v>
       </c>
     </row>
     <row r="44">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}}</t>
+          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}}</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2170,22 +2170,22 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.16168</v>
+        <v>0.16306</v>
       </c>
       <c r="F44" t="n">
-        <v>0.18358</v>
+        <v>0.18512</v>
       </c>
       <c r="G44" t="n">
-        <v>0.41434</v>
+        <v>0.41536</v>
       </c>
       <c r="H44" t="n">
-        <v>0.74154</v>
+        <v>0.74256</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2249800000000001</v>
+        <v>0.20856</v>
       </c>
       <c r="J44" t="n">
-        <v>0.5208999999999999</v>
+        <v>0.5281799999999999</v>
       </c>
     </row>
     <row r="45">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}}</t>
+          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}}</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2210,22 +2210,22 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.3866600000000001</v>
+        <v>0.37162</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4097399999999999</v>
+        <v>0.39332</v>
       </c>
       <c r="G45" t="n">
-        <v>0.57128</v>
+        <v>0.57026</v>
       </c>
       <c r="H45" t="n">
-        <v>0.8348799999999998</v>
+        <v>0.8276999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2249800000000001</v>
+        <v>0.20856</v>
       </c>
       <c r="J45" t="n">
-        <v>0.5208999999999999</v>
+        <v>0.5281799999999999</v>
       </c>
     </row>
     <row r="46">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}}</t>
+          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}}</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2250,22 +2250,22 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.9075599999999999</v>
+        <v>0.8997999999999999</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9219200000000001</v>
+        <v>0.91608</v>
       </c>
       <c r="G46" t="n">
-        <v>0.9277599999999999</v>
+        <v>0.9231</v>
       </c>
       <c r="H46" t="n">
         <v>0.9836599999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2249800000000001</v>
+        <v>0.20856</v>
       </c>
       <c r="J46" t="n">
-        <v>0.5208999999999999</v>
+        <v>0.5281799999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.268909, "environmental": 0.371359, "comfort": 0.160782, "practicality": 0.19895}</t>
+          <t>{"energy_cost": 0.268683, "environmental": 0.371046, "comfort": 0.16149, "practicality": 0.198782}</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2290,22 +2290,22 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.0393</v>
+        <v>0.03932</v>
       </c>
       <c r="F47" t="n">
-        <v>0.04102</v>
+        <v>0.04154</v>
       </c>
       <c r="G47" t="n">
-        <v>0.33846</v>
+        <v>0.33742</v>
       </c>
       <c r="H47" t="n">
-        <v>0.6707799999999999</v>
+        <v>0.67386</v>
       </c>
       <c r="I47" t="n">
-        <v>0.22908</v>
+        <v>0.2393200000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>0.6012000000000001</v>
+        <v>0.6018399999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.268909, "environmental": 0.371359, "comfort": 0.160782, "practicality": 0.19895}</t>
+          <t>{"energy_cost": 0.268683, "environmental": 0.371046, "comfort": 0.16149, "practicality": 0.198782}</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2330,22 +2330,22 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.26838</v>
+        <v>0.2786400000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>0.27948</v>
+        <v>0.28666</v>
       </c>
       <c r="G48" t="n">
-        <v>0.48</v>
+        <v>0.4851200000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>0.7702600000000001</v>
+        <v>0.7640800000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>0.22908</v>
+        <v>0.2393200000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>0.6012000000000001</v>
+        <v>0.6018399999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.268909, "environmental": 0.371359, "comfort": 0.160782, "practicality": 0.19895}</t>
+          <t>{"energy_cost": 0.268683, "environmental": 0.371046, "comfort": 0.16149, "practicality": 0.198782}</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2370,22 +2370,22 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.86958</v>
+        <v>0.88048</v>
       </c>
       <c r="F49" t="n">
-        <v>0.8876200000000001</v>
+        <v>0.89578</v>
       </c>
       <c r="G49" t="n">
-        <v>0.90572</v>
+        <v>0.91738</v>
       </c>
       <c r="H49" t="n">
-        <v>0.9812999999999998</v>
+        <v>0.98598</v>
       </c>
       <c r="I49" t="n">
-        <v>0.22908</v>
+        <v>0.2393200000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>0.6012000000000001</v>
+        <v>0.6018399999999999</v>
       </c>
     </row>
     <row r="50">
@@ -2410,22 +2410,22 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.05572000000000001</v>
+        <v>0.05778000000000001</v>
       </c>
       <c r="F50" t="n">
-        <v>0.05692000000000001</v>
+        <v>0.05898000000000001</v>
       </c>
       <c r="G50" t="n">
-        <v>0.34256</v>
+        <v>0.34668</v>
       </c>
       <c r="H50" t="n">
         <v>0.68206</v>
       </c>
       <c r="I50" t="n">
-        <v>0.25642</v>
+        <v>0.25982</v>
       </c>
       <c r="J50" t="n">
-        <v>0.5672999999999999</v>
+        <v>0.5641999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -2450,22 +2450,22 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.31214</v>
+        <v>0.3176</v>
       </c>
       <c r="F51" t="n">
-        <v>0.3318</v>
+        <v>0.33436</v>
       </c>
       <c r="G51" t="n">
-        <v>0.5117800000000001</v>
+        <v>0.5087200000000001</v>
       </c>
       <c r="H51" t="n">
-        <v>0.78768</v>
+        <v>0.78564</v>
       </c>
       <c r="I51" t="n">
-        <v>0.25642</v>
+        <v>0.25982</v>
       </c>
       <c r="J51" t="n">
-        <v>0.5672999999999999</v>
+        <v>0.5641999999999999</v>
       </c>
     </row>
     <row r="52">
@@ -2490,22 +2490,22 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.87944</v>
+        <v>0.8817999999999999</v>
       </c>
       <c r="F52" t="n">
-        <v>0.8985199999999999</v>
+        <v>0.8996600000000001</v>
       </c>
       <c r="G52" t="n">
-        <v>0.89394</v>
+        <v>0.8974399999999999</v>
       </c>
       <c r="H52" t="n">
         <v>0.98942</v>
       </c>
       <c r="I52" t="n">
-        <v>0.25642</v>
+        <v>0.25982</v>
       </c>
       <c r="J52" t="n">
-        <v>0.5672999999999999</v>
+        <v>0.5641999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -2530,22 +2530,22 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.004459999999999999</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F53" t="n">
-        <v>0.004119999999999999</v>
+        <v>0.006639999999999997</v>
       </c>
       <c r="G53" t="n">
-        <v>0.33024</v>
+        <v>0.33128</v>
       </c>
       <c r="H53" t="n">
-        <v>0.63486</v>
+        <v>0.63896</v>
       </c>
       <c r="I53" t="n">
-        <v>0.23658</v>
+        <v>0.24138</v>
       </c>
       <c r="J53" t="n">
-        <v>0.62146</v>
+        <v>0.6169600000000001</v>
       </c>
     </row>
     <row r="54">
@@ -2570,22 +2570,22 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.24104</v>
+        <v>0.24788</v>
       </c>
       <c r="F54" t="n">
-        <v>0.24974</v>
+        <v>0.25332</v>
       </c>
       <c r="G54" t="n">
-        <v>0.47074</v>
+        <v>0.47384</v>
       </c>
       <c r="H54" t="n">
-        <v>0.75588</v>
+        <v>0.75078</v>
       </c>
       <c r="I54" t="n">
-        <v>0.23658</v>
+        <v>0.24138</v>
       </c>
       <c r="J54" t="n">
-        <v>0.62146</v>
+        <v>0.6169600000000001</v>
       </c>
     </row>
     <row r="55">
@@ -2610,22 +2610,22 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.8625</v>
+        <v>0.8648400000000001</v>
       </c>
       <c r="F55" t="n">
-        <v>0.8793799999999999</v>
+        <v>0.8811199999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>0.89276</v>
+        <v>0.89162</v>
       </c>
       <c r="H55" t="n">
-        <v>0.97898</v>
+        <v>0.9836599999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>0.23658</v>
+        <v>0.24138</v>
       </c>
       <c r="J55" t="n">
-        <v>0.62146</v>
+        <v>0.6169600000000001</v>
       </c>
     </row>
     <row r="56">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}</t>
+          <t>{"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2650,22 +2650,22 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.05028000000000001</v>
+        <v>0.04684000000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>0.05744</v>
+        <v>0.0523</v>
       </c>
       <c r="G56" t="n">
-        <v>0.34154</v>
+        <v>0.3374199999999999</v>
       </c>
       <c r="H56" t="n">
-        <v>0.6677</v>
+        <v>0.66874</v>
       </c>
       <c r="I56" t="n">
-        <v>0.2304</v>
+        <v>0.24272</v>
       </c>
       <c r="J56" t="n">
-        <v>0.5647</v>
+        <v>0.5698399999999999</v>
       </c>
     </row>
     <row r="57">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}</t>
+          <t>{"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2690,22 +2690,22 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.28068</v>
+        <v>0.28956</v>
       </c>
       <c r="F57" t="n">
-        <v>0.29744</v>
+        <v>0.30204</v>
       </c>
       <c r="G57" t="n">
-        <v>0.4851200000000001</v>
+        <v>0.49024</v>
       </c>
       <c r="H57" t="n">
-        <v>0.7712600000000001</v>
+        <v>0.76514</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2304</v>
+        <v>0.24272</v>
       </c>
       <c r="J57" t="n">
-        <v>0.5647</v>
+        <v>0.5698399999999999</v>
       </c>
     </row>
     <row r="58">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}</t>
+          <t>{"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2730,22 +2730,22 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.8453799999999999</v>
+        <v>0.8593999999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>0.8689</v>
+        <v>0.8788199999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>0.8648199999999999</v>
+        <v>0.8823399999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>0.98016</v>
+        <v>0.9836599999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2304</v>
+        <v>0.24272</v>
       </c>
       <c r="J58" t="n">
-        <v>0.5647</v>
+        <v>0.5698399999999999</v>
       </c>
     </row>
     <row r="59">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}}</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2770,22 +2770,22 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.03932</v>
+        <v>0.04274</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0364</v>
+        <v>0.03948</v>
       </c>
       <c r="G59" t="n">
-        <v>0.34562</v>
+        <v>0.3477</v>
       </c>
       <c r="H59" t="n">
-        <v>0.67284</v>
+        <v>0.6769400000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>0.23452</v>
+        <v>0.2393</v>
       </c>
       <c r="J59" t="n">
-        <v>0.6103799999999999</v>
+        <v>0.60608</v>
       </c>
     </row>
     <row r="60">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}}</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2810,22 +2810,22 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.27384</v>
+        <v>0.28204</v>
       </c>
       <c r="F60" t="n">
-        <v>0.28566</v>
+        <v>0.29128</v>
       </c>
       <c r="G60" t="n">
-        <v>0.49024</v>
+        <v>0.4964200000000001</v>
       </c>
       <c r="H60" t="n">
-        <v>0.77846</v>
+        <v>0.77128</v>
       </c>
       <c r="I60" t="n">
-        <v>0.23452</v>
+        <v>0.2393</v>
       </c>
       <c r="J60" t="n">
-        <v>0.6103799999999999</v>
+        <v>0.60608</v>
       </c>
     </row>
     <row r="61">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}}</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2850,22 +2850,22 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.88422</v>
+        <v>0.88812</v>
       </c>
       <c r="F61" t="n">
-        <v>0.9009</v>
+        <v>0.90388</v>
       </c>
       <c r="G61" t="n">
-        <v>0.93008</v>
+        <v>0.9313</v>
       </c>
       <c r="H61" t="n">
-        <v>0.9859599999999998</v>
+        <v>0.9906599999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>0.23452</v>
+        <v>0.2393</v>
       </c>
       <c r="J61" t="n">
-        <v>0.6103799999999999</v>
+        <v>0.60608</v>
       </c>
     </row>
     <row r="62">
@@ -2902,10 +2902,10 @@
         <v>0.67798</v>
       </c>
       <c r="I62" t="n">
-        <v>0.29336</v>
+        <v>0.29542</v>
       </c>
       <c r="J62" t="n">
-        <v>0.5467200000000001</v>
+        <v>0.54542</v>
       </c>
     </row>
     <row r="63">
@@ -2930,22 +2930,22 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.36548</v>
+        <v>0.36754</v>
       </c>
       <c r="F63" t="n">
-        <v>0.3845999999999999</v>
+        <v>0.38564</v>
       </c>
       <c r="G63" t="n">
-        <v>0.5518000000000001</v>
+        <v>0.5456199999999999</v>
       </c>
       <c r="H63" t="n">
-        <v>0.8194799999999999</v>
+        <v>0.8154</v>
       </c>
       <c r="I63" t="n">
-        <v>0.29336</v>
+        <v>0.29542</v>
       </c>
       <c r="J63" t="n">
-        <v>0.5467200000000001</v>
+        <v>0.54542</v>
       </c>
     </row>
     <row r="64">
@@ -2970,22 +2970,22 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.9122</v>
+        <v>0.91296</v>
       </c>
       <c r="F64" t="n">
-        <v>0.9224399999999999</v>
+        <v>0.92302</v>
       </c>
       <c r="G64" t="n">
-        <v>0.93244</v>
+        <v>0.9335800000000001</v>
       </c>
       <c r="H64" t="n">
         <v>0.9812799999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>0.29336</v>
+        <v>0.29542</v>
       </c>
       <c r="J64" t="n">
-        <v>0.5467200000000001</v>
+        <v>0.54542</v>
       </c>
     </row>
     <row r="65">
@@ -3022,10 +3022,10 @@
         <v>0.6882200000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>0.25368</v>
+        <v>0.25574</v>
       </c>
       <c r="J65" t="n">
-        <v>0.5893999999999999</v>
+        <v>0.5881000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -3050,22 +3050,22 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.31966</v>
+        <v>0.32172</v>
       </c>
       <c r="F66" t="n">
-        <v>0.34616</v>
+        <v>0.34718</v>
       </c>
       <c r="G66" t="n">
-        <v>0.51384</v>
+        <v>0.5076799999999999</v>
       </c>
       <c r="H66" t="n">
-        <v>0.8</v>
+        <v>0.7959000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>0.25368</v>
+        <v>0.25574</v>
       </c>
       <c r="J66" t="n">
-        <v>0.5893999999999999</v>
+        <v>0.5881000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -3090,22 +3090,22 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.90906</v>
+        <v>0.9098200000000001</v>
       </c>
       <c r="F67" t="n">
-        <v>0.92012</v>
+        <v>0.9206800000000002</v>
       </c>
       <c r="G67" t="n">
-        <v>0.92078</v>
+        <v>0.9219200000000001</v>
       </c>
       <c r="H67" t="n">
         <v>0.9812799999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>0.25368</v>
+        <v>0.25574</v>
       </c>
       <c r="J67" t="n">
-        <v>0.5893999999999999</v>
+        <v>0.5881000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -3142,10 +3142,10 @@
         <v>0.70974</v>
       </c>
       <c r="I68" t="n">
-        <v>0.13058</v>
+        <v>0.1142</v>
       </c>
       <c r="J68" t="n">
-        <v>0.6389999999999998</v>
+        <v>0.6468400000000001</v>
       </c>
     </row>
     <row r="69">
@@ -3170,22 +3170,22 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.24374</v>
+        <v>0.22736</v>
       </c>
       <c r="F69" t="n">
-        <v>0.26052</v>
+        <v>0.24254</v>
       </c>
       <c r="G69" t="n">
-        <v>0.46872</v>
+        <v>0.4615600000000001</v>
       </c>
       <c r="H69" t="n">
-        <v>0.7558999999999999</v>
+        <v>0.7507600000000001</v>
       </c>
       <c r="I69" t="n">
-        <v>0.13058</v>
+        <v>0.1142</v>
       </c>
       <c r="J69" t="n">
-        <v>0.6389999999999998</v>
+        <v>0.6468400000000001</v>
       </c>
     </row>
     <row r="70">
@@ -3210,22 +3210,22 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.8827399999999999</v>
+        <v>0.8742000000000001</v>
       </c>
       <c r="F70" t="n">
-        <v>0.9026999999999999</v>
+        <v>0.89688</v>
       </c>
       <c r="G70" t="n">
-        <v>0.91264</v>
+        <v>0.90564</v>
       </c>
       <c r="H70" t="n">
         <v>0.9836599999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>0.13058</v>
+        <v>0.1142</v>
       </c>
       <c r="J70" t="n">
-        <v>0.6389999999999998</v>
+        <v>0.6468400000000001</v>
       </c>
     </row>
     <row r="71">
@@ -3250,22 +3250,22 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.04072</v>
+        <v>0.04274</v>
       </c>
       <c r="F71" t="n">
-        <v>0.03793999999999999</v>
+        <v>0.04049999999999999</v>
       </c>
       <c r="G71" t="n">
-        <v>0.34562</v>
+        <v>0.34668</v>
       </c>
       <c r="H71" t="n">
-        <v>0.6748800000000001</v>
+        <v>0.679</v>
       </c>
       <c r="I71" t="n">
-        <v>0.23176</v>
+        <v>0.23726</v>
       </c>
       <c r="J71" t="n">
-        <v>0.6125</v>
+        <v>0.605</v>
       </c>
     </row>
     <row r="72">
@@ -3290,22 +3290,22 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.27248</v>
+        <v>0.28</v>
       </c>
       <c r="F72" t="n">
-        <v>0.28462</v>
+        <v>0.28974</v>
       </c>
       <c r="G72" t="n">
-        <v>0.4892</v>
+        <v>0.49332</v>
       </c>
       <c r="H72" t="n">
-        <v>0.77846</v>
+        <v>0.77128</v>
       </c>
       <c r="I72" t="n">
-        <v>0.23176</v>
+        <v>0.23726</v>
       </c>
       <c r="J72" t="n">
-        <v>0.6125</v>
+        <v>0.605</v>
       </c>
     </row>
     <row r="73">
@@ -3330,22 +3330,22 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.88498</v>
+        <v>0.885</v>
       </c>
       <c r="F73" t="n">
-        <v>0.90266</v>
+        <v>0.9026799999999999</v>
       </c>
       <c r="G73" t="n">
-        <v>0.9289400000000001</v>
+        <v>0.92432</v>
       </c>
       <c r="H73" t="n">
-        <v>0.9882799999999999</v>
+        <v>0.9929600000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>0.23176</v>
+        <v>0.23726</v>
       </c>
       <c r="J73" t="n">
-        <v>0.6125</v>
+        <v>0.605</v>
       </c>
     </row>
     <row r="74">
@@ -3382,10 +3382,10 @@
         <v>0.6772799999999999</v>
       </c>
       <c r="I74" t="n">
-        <v>0.19686</v>
+        <v>0.19822</v>
       </c>
       <c r="J74" t="n">
-        <v>0.67326</v>
+        <v>0.6718999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -3410,22 +3410,22 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.20684</v>
+        <v>0.2082</v>
       </c>
       <c r="F75" t="n">
-        <v>0.22204</v>
+        <v>0.22412</v>
       </c>
       <c r="G75" t="n">
-        <v>0.46976</v>
+        <v>0.46566</v>
       </c>
       <c r="H75" t="n">
-        <v>0.7682</v>
+        <v>0.7805199999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>0.19686</v>
+        <v>0.19822</v>
       </c>
       <c r="J75" t="n">
-        <v>0.67326</v>
+        <v>0.6718999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -3462,10 +3462,10 @@
         <v>0.96918</v>
       </c>
       <c r="I76" t="n">
-        <v>0.19686</v>
+        <v>0.19822</v>
       </c>
       <c r="J76" t="n">
-        <v>0.67326</v>
+        <v>0.6718999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3490,22 +3490,22 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.04628</v>
+        <v>0.04426</v>
       </c>
       <c r="F77" t="n">
-        <v>0.04886</v>
+        <v>0.04681999999999999</v>
       </c>
       <c r="G77" t="n">
-        <v>0.32684</v>
+        <v>0.32478</v>
       </c>
       <c r="H77" t="n">
-        <v>0.704</v>
+        <v>0.70194</v>
       </c>
       <c r="I77" t="n">
-        <v>0.15646</v>
+        <v>0.1448</v>
       </c>
       <c r="J77" t="n">
-        <v>0.6527200000000001</v>
+        <v>0.6629599999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3530,22 +3530,22 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.20274</v>
+        <v>0.18906</v>
       </c>
       <c r="F78" t="n">
-        <v>0.2154</v>
+        <v>0.20412</v>
       </c>
       <c r="G78" t="n">
-        <v>0.46666</v>
+        <v>0.4471999999999999</v>
       </c>
       <c r="H78" t="n">
-        <v>0.7722999999999999</v>
+        <v>0.7764</v>
       </c>
       <c r="I78" t="n">
-        <v>0.15646</v>
+        <v>0.1448</v>
       </c>
       <c r="J78" t="n">
-        <v>0.6527200000000001</v>
+        <v>0.6629599999999999</v>
       </c>
     </row>
     <row r="79">
@@ -3570,22 +3570,22 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.8554600000000001</v>
+        <v>0.8520199999999999</v>
       </c>
       <c r="F79" t="n">
-        <v>0.87052</v>
+        <v>0.86798</v>
       </c>
       <c r="G79" t="n">
-        <v>0.88182</v>
+        <v>0.87668</v>
       </c>
       <c r="H79" t="n">
         <v>0.96302</v>
       </c>
       <c r="I79" t="n">
-        <v>0.15646</v>
+        <v>0.1448</v>
       </c>
       <c r="J79" t="n">
-        <v>0.6527200000000001</v>
+        <v>0.6629599999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3610,10 +3610,10 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>-0.00168</v>
+        <v>-0.0024</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.00406</v>
+        <v>-0.0046</v>
       </c>
       <c r="G80" t="n">
         <v>0.29602</v>
@@ -3622,10 +3622,10 @@
         <v>0.68548</v>
       </c>
       <c r="I80" t="n">
-        <v>0.18936</v>
+        <v>0.19762</v>
       </c>
       <c r="J80" t="n">
-        <v>0.69858</v>
+        <v>0.6910400000000001</v>
       </c>
     </row>
     <row r="81">
@@ -3650,22 +3650,22 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.18768</v>
+        <v>0.19522</v>
       </c>
       <c r="F81" t="n">
-        <v>0.20308</v>
+        <v>0.2123</v>
       </c>
       <c r="G81" t="n">
-        <v>0.45128</v>
+        <v>0.45436</v>
       </c>
       <c r="H81" t="n">
-        <v>0.74974</v>
+        <v>0.77536</v>
       </c>
       <c r="I81" t="n">
-        <v>0.18936</v>
+        <v>0.19762</v>
       </c>
       <c r="J81" t="n">
-        <v>0.69858</v>
+        <v>0.6910400000000001</v>
       </c>
     </row>
     <row r="82">
@@ -3696,16 +3696,16 @@
         <v>0.8962</v>
       </c>
       <c r="G82" t="n">
-        <v>0.9116200000000001</v>
+        <v>0.91676</v>
       </c>
       <c r="H82" t="n">
         <v>0.9804600000000001</v>
       </c>
       <c r="I82" t="n">
-        <v>0.18936</v>
+        <v>0.19762</v>
       </c>
       <c r="J82" t="n">
-        <v>0.69858</v>
+        <v>0.6910400000000001</v>
       </c>
     </row>
     <row r="83">
@@ -3730,22 +3730,22 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.02162</v>
+        <v>0.0189</v>
       </c>
       <c r="F83" t="n">
-        <v>0.0206</v>
+        <v>0.01752</v>
       </c>
       <c r="G83" t="n">
-        <v>0.31042</v>
+        <v>0.30836</v>
       </c>
       <c r="H83" t="n">
-        <v>0.6855</v>
+        <v>0.68346</v>
       </c>
       <c r="I83" t="n">
-        <v>0.20506</v>
+        <v>0.19272</v>
       </c>
       <c r="J83" t="n">
-        <v>0.6466000000000001</v>
+        <v>0.6547800000000001</v>
       </c>
     </row>
     <row r="84">
@@ -3770,22 +3770,22 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.22668</v>
+        <v>0.21162</v>
       </c>
       <c r="F84" t="n">
-        <v>0.24</v>
+        <v>0.22718</v>
       </c>
       <c r="G84" t="n">
-        <v>0.48206</v>
+        <v>0.46156</v>
       </c>
       <c r="H84" t="n">
-        <v>0.78462</v>
+        <v>0.78872</v>
       </c>
       <c r="I84" t="n">
-        <v>0.20506</v>
+        <v>0.19272</v>
       </c>
       <c r="J84" t="n">
-        <v>0.6466000000000001</v>
+        <v>0.6547800000000001</v>
       </c>
     </row>
     <row r="85">
@@ -3810,22 +3810,22 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.8732800000000001</v>
+        <v>0.8664000000000002</v>
       </c>
       <c r="F85" t="n">
-        <v>0.8880000000000001</v>
+        <v>0.88286</v>
       </c>
       <c r="G85" t="n">
-        <v>0.8879999999999999</v>
+        <v>0.8828799999999999</v>
       </c>
       <c r="H85" t="n">
         <v>0.9712400000000001</v>
       </c>
       <c r="I85" t="n">
-        <v>0.20506</v>
+        <v>0.19272</v>
       </c>
       <c r="J85" t="n">
-        <v>0.6466000000000001</v>
+        <v>0.6547800000000001</v>
       </c>
     </row>
     <row r="86">
@@ -3862,10 +3862,10 @@
         <v>0.68546</v>
       </c>
       <c r="I86" t="n">
-        <v>0.18388</v>
+        <v>0.19962</v>
       </c>
       <c r="J86" t="n">
-        <v>0.7013199999999999</v>
+        <v>0.6889999999999998</v>
       </c>
     </row>
     <row r="87">
@@ -3890,22 +3890,22 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.18632</v>
+        <v>0.20206</v>
       </c>
       <c r="F87" t="n">
-        <v>0.20256</v>
+        <v>0.2195</v>
       </c>
       <c r="G87" t="n">
-        <v>0.45128</v>
+        <v>0.4564199999999999</v>
       </c>
       <c r="H87" t="n">
-        <v>0.7487</v>
+        <v>0.77846</v>
       </c>
       <c r="I87" t="n">
-        <v>0.18388</v>
+        <v>0.19962</v>
       </c>
       <c r="J87" t="n">
-        <v>0.7013199999999999</v>
+        <v>0.6889999999999998</v>
       </c>
     </row>
     <row r="88">
@@ -3930,22 +3930,22 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.88764</v>
+        <v>0.8910599999999999</v>
       </c>
       <c r="F88" t="n">
-        <v>0.8957000000000001</v>
+        <v>0.8982599999999999</v>
       </c>
       <c r="G88" t="n">
-        <v>0.9033999999999999</v>
+        <v>0.90854</v>
       </c>
       <c r="H88" t="n">
         <v>0.9774</v>
       </c>
       <c r="I88" t="n">
-        <v>0.18388</v>
+        <v>0.19962</v>
       </c>
       <c r="J88" t="n">
-        <v>0.7013199999999999</v>
+        <v>0.6889999999999998</v>
       </c>
     </row>
     <row r="89">
@@ -3970,22 +3970,22 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>-0.0051</v>
+        <v>-0.0058</v>
       </c>
       <c r="F89" t="n">
-        <v>-0.007140000000000001</v>
+        <v>-0.00872</v>
       </c>
       <c r="G89" t="n">
-        <v>0.29088</v>
+        <v>0.29292</v>
       </c>
       <c r="H89" t="n">
-        <v>0.6804</v>
+        <v>0.6762599999999999</v>
       </c>
       <c r="I89" t="n">
-        <v>0.2058</v>
+        <v>0.21196</v>
       </c>
       <c r="J89" t="n">
-        <v>0.6883</v>
+        <v>0.67942</v>
       </c>
     </row>
     <row r="90">
@@ -4010,22 +4010,22 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.2007</v>
+        <v>0.20616</v>
       </c>
       <c r="F90" t="n">
-        <v>0.21692</v>
+        <v>0.22408</v>
       </c>
       <c r="G90" t="n">
-        <v>0.44616</v>
+        <v>0.4482399999999999</v>
       </c>
       <c r="H90" t="n">
-        <v>0.7579400000000001</v>
+        <v>0.77744</v>
       </c>
       <c r="I90" t="n">
-        <v>0.2058</v>
+        <v>0.21196</v>
       </c>
       <c r="J90" t="n">
-        <v>0.6883</v>
+        <v>0.67942</v>
       </c>
     </row>
     <row r="91">
@@ -4050,22 +4050,22 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.889</v>
+        <v>0.88558</v>
       </c>
       <c r="F91" t="n">
-        <v>0.8987999999999999</v>
+        <v>0.89362</v>
       </c>
       <c r="G91" t="n">
         <v>0.9136799999999999</v>
       </c>
       <c r="H91" t="n">
-        <v>0.9815000000000002</v>
+        <v>0.97638</v>
       </c>
       <c r="I91" t="n">
-        <v>0.2058</v>
+        <v>0.21196</v>
       </c>
       <c r="J91" t="n">
-        <v>0.6883</v>
+        <v>0.67942</v>
       </c>
     </row>
     <row r="92">
@@ -4090,22 +4090,22 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.0525</v>
+        <v>0.05044</v>
       </c>
       <c r="F92" t="n">
-        <v>0.05404</v>
+        <v>0.05198000000000001</v>
       </c>
       <c r="G92" t="n">
-        <v>0.3309799999999999</v>
+        <v>0.32892</v>
       </c>
       <c r="H92" t="n">
-        <v>0.7009200000000001</v>
+        <v>0.6988800000000001</v>
       </c>
       <c r="I92" t="n">
-        <v>0.14478</v>
+        <v>0.12972</v>
       </c>
       <c r="J92" t="n">
-        <v>0.63212</v>
+        <v>0.64584</v>
       </c>
     </row>
     <row r="93">
@@ -4130,22 +4130,22 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.19728</v>
+        <v>0.18016</v>
       </c>
       <c r="F93" t="n">
-        <v>0.2072</v>
+        <v>0.19024</v>
       </c>
       <c r="G93" t="n">
-        <v>0.4646</v>
+        <v>0.4482200000000001</v>
       </c>
       <c r="H93" t="n">
-        <v>0.76822</v>
+        <v>0.76716</v>
       </c>
       <c r="I93" t="n">
-        <v>0.14478</v>
+        <v>0.12972</v>
       </c>
       <c r="J93" t="n">
-        <v>0.63212</v>
+        <v>0.64584</v>
       </c>
     </row>
     <row r="94">
@@ -4170,22 +4170,22 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.8294</v>
+        <v>0.826</v>
       </c>
       <c r="F94" t="n">
-        <v>0.8478999999999999</v>
+        <v>0.84536</v>
       </c>
       <c r="G94" t="n">
-        <v>0.8705200000000002</v>
+        <v>0.86538</v>
       </c>
       <c r="H94" t="n">
         <v>0.9578599999999999</v>
       </c>
       <c r="I94" t="n">
-        <v>0.14478</v>
+        <v>0.12972</v>
       </c>
       <c r="J94" t="n">
-        <v>0.63212</v>
+        <v>0.64584</v>
       </c>
     </row>
     <row r="95">
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>-0.00784</v>
+        <v>-0.008540000000000001</v>
       </c>
       <c r="F95" t="n">
-        <v>-0.01232</v>
+        <v>-0.01384</v>
       </c>
       <c r="G95" t="n">
         <v>0.28986</v>
@@ -4222,10 +4222,10 @@
         <v>0.67726</v>
       </c>
       <c r="I95" t="n">
-        <v>0.19622</v>
+        <v>0.20376</v>
       </c>
       <c r="J95" t="n">
-        <v>0.6978800000000001</v>
+        <v>0.6855800000000001</v>
       </c>
     </row>
     <row r="96">
@@ -4250,22 +4250,22 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.18838</v>
+        <v>0.19522</v>
       </c>
       <c r="F96" t="n">
-        <v>0.20208</v>
+        <v>0.20768</v>
       </c>
       <c r="G96" t="n">
-        <v>0.45334</v>
+        <v>0.45538</v>
       </c>
       <c r="H96" t="n">
-        <v>0.7487200000000001</v>
+        <v>0.7651199999999999</v>
       </c>
       <c r="I96" t="n">
-        <v>0.19622</v>
+        <v>0.20376</v>
       </c>
       <c r="J96" t="n">
-        <v>0.6978800000000001</v>
+        <v>0.6855800000000001</v>
       </c>
     </row>
     <row r="97">
@@ -4290,22 +4290,22 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.88626</v>
+        <v>0.8808</v>
       </c>
       <c r="F97" t="n">
-        <v>0.8997999999999999</v>
+        <v>0.8936399999999999</v>
       </c>
       <c r="G97" t="n">
         <v>0.9095799999999998</v>
       </c>
       <c r="H97" t="n">
-        <v>0.97638</v>
+        <v>0.9712200000000001</v>
       </c>
       <c r="I97" t="n">
-        <v>0.19622</v>
+        <v>0.20376</v>
       </c>
       <c r="J97" t="n">
-        <v>0.6978800000000001</v>
+        <v>0.6855800000000001</v>
       </c>
     </row>
     <row r="98">
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.0367</v>
+        <v>0.03602</v>
       </c>
       <c r="F98" t="n">
-        <v>0.03862</v>
+        <v>0.0376</v>
       </c>
       <c r="G98" t="n">
         <v>0.32276</v>
@@ -4342,10 +4342,10 @@
         <v>0.6968</v>
       </c>
       <c r="I98" t="n">
-        <v>0.18108</v>
+        <v>0.17356</v>
       </c>
       <c r="J98" t="n">
-        <v>0.6603</v>
+        <v>0.66438</v>
       </c>
     </row>
     <row r="99">
@@ -4370,22 +4370,22 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.21778</v>
+        <v>0.20958</v>
       </c>
       <c r="F99" t="n">
-        <v>0.2308</v>
+        <v>0.22616</v>
       </c>
       <c r="G99" t="n">
-        <v>0.47076</v>
+        <v>0.4564199999999999</v>
       </c>
       <c r="H99" t="n">
-        <v>0.7805</v>
+        <v>0.78664</v>
       </c>
       <c r="I99" t="n">
-        <v>0.18108</v>
+        <v>0.17356</v>
       </c>
       <c r="J99" t="n">
-        <v>0.6603</v>
+        <v>0.66438</v>
       </c>
     </row>
     <row r="100">
@@ -4410,22 +4410,22 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.87808</v>
+        <v>0.87396</v>
       </c>
       <c r="F100" t="n">
-        <v>0.89108</v>
+        <v>0.8874599999999999</v>
       </c>
       <c r="G100" t="n">
         <v>0.8972599999999999</v>
       </c>
       <c r="H100" t="n">
-        <v>0.9702</v>
+        <v>0.9691599999999999</v>
       </c>
       <c r="I100" t="n">
-        <v>0.18108</v>
+        <v>0.17356</v>
       </c>
       <c r="J100" t="n">
-        <v>0.6603</v>
+        <v>0.66438</v>
       </c>
     </row>
     <row r="101">
@@ -4450,10 +4450,10 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>-0.02702</v>
+        <v>-0.02772</v>
       </c>
       <c r="F101" t="n">
-        <v>-0.03184</v>
+        <v>-0.03234</v>
       </c>
       <c r="G101" t="n">
         <v>0.2878</v>
@@ -4462,10 +4462,10 @@
         <v>0.6752400000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>0.26532</v>
+        <v>0.25304</v>
       </c>
       <c r="J101" t="n">
-        <v>0.6514</v>
+        <v>0.65408</v>
       </c>
     </row>
     <row r="102">
@@ -4490,22 +4490,22 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.2383</v>
+        <v>0.22532</v>
       </c>
       <c r="F102" t="n">
-        <v>0.25846</v>
+        <v>0.24154</v>
       </c>
       <c r="G102" t="n">
-        <v>0.47182</v>
+        <v>0.46154</v>
       </c>
       <c r="H102" t="n">
-        <v>0.76922</v>
+        <v>0.77642</v>
       </c>
       <c r="I102" t="n">
-        <v>0.26532</v>
+        <v>0.25304</v>
       </c>
       <c r="J102" t="n">
-        <v>0.6514</v>
+        <v>0.65408</v>
       </c>
     </row>
     <row r="103">
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.8897</v>
+        <v>0.8794000000000001</v>
       </c>
       <c r="F103" t="n">
-        <v>0.91112</v>
+        <v>0.9034000000000001</v>
       </c>
       <c r="G103" t="n">
         <v>0.8951799999999999</v>
@@ -4542,10 +4542,10 @@
         <v>0.99382</v>
       </c>
       <c r="I103" t="n">
-        <v>0.26532</v>
+        <v>0.25304</v>
       </c>
       <c r="J103" t="n">
-        <v>0.6514</v>
+        <v>0.65408</v>
       </c>
     </row>
     <row r="104">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.194172, "environmental": 0.131673, "comfort": 0.401912, "practicality": 0.272243}</t>
+          <t>{"energy_cost": 0.1943, "environmental": 0.131354, "comfort": 0.403745, "practicality": 0.2706}</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4582,10 +4582,10 @@
         <v>0.66596</v>
       </c>
       <c r="I104" t="n">
-        <v>0.25914</v>
+        <v>0.26666</v>
       </c>
       <c r="J104" t="n">
-        <v>0.6815999999999998</v>
+        <v>0.6959999999999998</v>
       </c>
     </row>
     <row r="105">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.194172, "environmental": 0.131673, "comfort": 0.401912, "practicality": 0.272243}</t>
+          <t>{"energy_cost": 0.1943, "environmental": 0.131354, "comfort": 0.403745, "practicality": 0.2706}</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4610,22 +4610,22 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.25948</v>
+        <v>0.267</v>
       </c>
       <c r="F105" t="n">
-        <v>0.28104</v>
+        <v>0.28716</v>
       </c>
       <c r="G105" t="n">
-        <v>0.49948</v>
+        <v>0.49844</v>
       </c>
       <c r="H105" t="n">
-        <v>0.7743399999999999</v>
+        <v>0.78462</v>
       </c>
       <c r="I105" t="n">
-        <v>0.25914</v>
+        <v>0.26666</v>
       </c>
       <c r="J105" t="n">
-        <v>0.6815999999999998</v>
+        <v>0.6959999999999998</v>
       </c>
     </row>
     <row r="106">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.194172, "environmental": 0.131673, "comfort": 0.401912, "practicality": 0.272243}</t>
+          <t>{"energy_cost": 0.1943, "environmental": 0.131354, "comfort": 0.403745, "practicality": 0.2706}</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4650,22 +4650,22 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.9410799999999998</v>
+        <v>0.9629999999999999</v>
       </c>
       <c r="F106" t="n">
-        <v>0.9558200000000001</v>
+        <v>0.97226</v>
       </c>
       <c r="G106" t="n">
-        <v>0.9445399999999999</v>
+        <v>0.9753399999999999</v>
       </c>
       <c r="H106" t="n">
         <v>1</v>
       </c>
       <c r="I106" t="n">
-        <v>0.25914</v>
+        <v>0.26666</v>
       </c>
       <c r="J106" t="n">
-        <v>0.6815999999999998</v>
+        <v>0.6959999999999998</v>
       </c>
     </row>
     <row r="107">
@@ -4702,10 +4702,10 @@
         <v>0.6968</v>
       </c>
       <c r="I107" t="n">
-        <v>0.21526</v>
+        <v>0.218</v>
       </c>
       <c r="J107" t="n">
-        <v>0.6878200000000001</v>
+        <v>0.70222</v>
       </c>
     </row>
     <row r="108">
@@ -4730,22 +4730,22 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.2793</v>
+        <v>0.28204</v>
       </c>
       <c r="F108" t="n">
-        <v>0.30304</v>
+        <v>0.30106</v>
       </c>
       <c r="G108" t="n">
-        <v>0.5179400000000001</v>
+        <v>0.51588</v>
       </c>
       <c r="H108" t="n">
-        <v>0.78872</v>
+        <v>0.7825599999999999</v>
       </c>
       <c r="I108" t="n">
-        <v>0.21526</v>
+        <v>0.218</v>
       </c>
       <c r="J108" t="n">
-        <v>0.6878200000000001</v>
+        <v>0.70222</v>
       </c>
     </row>
     <row r="109">
@@ -4770,22 +4770,22 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.9671200000000001</v>
+        <v>0.9842599999999999</v>
       </c>
       <c r="F109" t="n">
-        <v>0.9753399999999999</v>
+        <v>0.9881800000000001</v>
       </c>
       <c r="G109" t="n">
-        <v>0.9661</v>
+        <v>0.99176</v>
       </c>
       <c r="H109" t="n">
         <v>1</v>
       </c>
       <c r="I109" t="n">
-        <v>0.21526</v>
+        <v>0.218</v>
       </c>
       <c r="J109" t="n">
-        <v>0.6878200000000001</v>
+        <v>0.70222</v>
       </c>
     </row>
     <row r="110">
@@ -4822,10 +4822,10 @@
         <v>0.6648799999999999</v>
       </c>
       <c r="I110" t="n">
-        <v>0.24006</v>
+        <v>0.238</v>
       </c>
       <c r="J110" t="n">
-        <v>0.7109799999999998</v>
+        <v>0.7295</v>
       </c>
     </row>
     <row r="111">
@@ -4850,22 +4850,22 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.23146</v>
+        <v>0.2294</v>
       </c>
       <c r="F111" t="n">
-        <v>0.25232</v>
+        <v>0.24974</v>
       </c>
       <c r="G111" t="n">
-        <v>0.49232</v>
+        <v>0.4759</v>
       </c>
       <c r="H111" t="n">
-        <v>0.76922</v>
+        <v>0.7712600000000001</v>
       </c>
       <c r="I111" t="n">
-        <v>0.24006</v>
+        <v>0.238</v>
       </c>
       <c r="J111" t="n">
-        <v>0.7109799999999998</v>
+        <v>0.7295</v>
       </c>
     </row>
     <row r="112">
@@ -4890,22 +4890,22 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.9424399999999998</v>
+        <v>0.9589000000000001</v>
       </c>
       <c r="F112" t="n">
-        <v>0.95684</v>
+        <v>0.9691600000000001</v>
       </c>
       <c r="G112" t="n">
-        <v>0.9548</v>
+        <v>0.9599</v>
       </c>
       <c r="H112" t="n">
         <v>1</v>
       </c>
       <c r="I112" t="n">
-        <v>0.24006</v>
+        <v>0.238</v>
       </c>
       <c r="J112" t="n">
-        <v>0.7109799999999998</v>
+        <v>0.7295</v>
       </c>
     </row>
     <row r="113">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}</t>
+          <t>{"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4930,22 +4930,22 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>-0.02364</v>
+        <v>-0.0257</v>
       </c>
       <c r="F113" t="n">
-        <v>-0.03134</v>
+        <v>-0.03236</v>
       </c>
       <c r="G113" t="n">
-        <v>0.29808</v>
+        <v>0.29706</v>
       </c>
       <c r="H113" t="n">
-        <v>0.66082</v>
+        <v>0.65878</v>
       </c>
       <c r="I113" t="n">
-        <v>0.26056</v>
+        <v>0.23938</v>
       </c>
       <c r="J113" t="n">
-        <v>0.6418200000000001</v>
+        <v>0.66164</v>
       </c>
     </row>
     <row r="114">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}</t>
+          <t>{"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4970,22 +4970,22 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.23692</v>
+        <v>0.21368</v>
       </c>
       <c r="F114" t="n">
-        <v>0.2512800000000001</v>
+        <v>0.22616</v>
       </c>
       <c r="G114" t="n">
-        <v>0.48</v>
+        <v>0.46566</v>
       </c>
       <c r="H114" t="n">
         <v>0.77024</v>
       </c>
       <c r="I114" t="n">
-        <v>0.26056</v>
+        <v>0.23938</v>
       </c>
       <c r="J114" t="n">
-        <v>0.6418200000000001</v>
+        <v>0.66164</v>
       </c>
     </row>
     <row r="115">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}</t>
+          <t>{"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5010,22 +5010,22 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.87874</v>
+        <v>0.87532</v>
       </c>
       <c r="F115" t="n">
-        <v>0.89978</v>
+        <v>0.89878</v>
       </c>
       <c r="G115" t="n">
-        <v>0.8859600000000001</v>
+        <v>0.8839</v>
       </c>
       <c r="H115" t="n">
-        <v>0.9886800000000001</v>
+        <v>0.99382</v>
       </c>
       <c r="I115" t="n">
-        <v>0.26056</v>
+        <v>0.23938</v>
       </c>
       <c r="J115" t="n">
-        <v>0.6418200000000001</v>
+        <v>0.66164</v>
       </c>
     </row>
     <row r="116">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}}</t>
+          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}}</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5062,10 +5062,10 @@
         <v>0.6793199999999999</v>
       </c>
       <c r="I116" t="n">
-        <v>0.22962</v>
+        <v>0.20636</v>
       </c>
       <c r="J116" t="n">
-        <v>0.6541999999999999</v>
+        <v>0.67334</v>
       </c>
     </row>
     <row r="117">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}}</t>
+          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}}</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5090,22 +5090,22 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.27112</v>
+        <v>0.24786</v>
       </c>
       <c r="F117" t="n">
-        <v>0.28822</v>
+        <v>0.2640999999999999</v>
       </c>
       <c r="G117" t="n">
-        <v>0.5118</v>
+        <v>0.4995</v>
       </c>
       <c r="H117" t="n">
-        <v>0.7774</v>
+        <v>0.77844</v>
       </c>
       <c r="I117" t="n">
-        <v>0.22962</v>
+        <v>0.20636</v>
       </c>
       <c r="J117" t="n">
-        <v>0.6541999999999999</v>
+        <v>0.67334</v>
       </c>
     </row>
     <row r="118">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}}</t>
+          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}}</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5130,22 +5130,22 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.9253199999999999</v>
+        <v>0.9212</v>
       </c>
       <c r="F118" t="n">
-        <v>0.9352599999999999</v>
+        <v>0.9337</v>
       </c>
       <c r="G118" t="n">
-        <v>0.92394</v>
+        <v>0.92188</v>
       </c>
       <c r="H118" t="n">
-        <v>0.9886800000000001</v>
+        <v>0.99382</v>
       </c>
       <c r="I118" t="n">
-        <v>0.22962</v>
+        <v>0.20636</v>
       </c>
       <c r="J118" t="n">
-        <v>0.6541999999999999</v>
+        <v>0.67334</v>
       </c>
     </row>
     <row r="119">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.268909, "environmental": 0.371359, "comfort": 0.160782, "practicality": 0.19895}</t>
+          <t>{"energy_cost": 0.268683, "environmental": 0.371046, "comfort": 0.16149, "practicality": 0.198782}</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5170,22 +5170,22 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.005840000000000001</v>
+        <v>0.00448</v>
       </c>
       <c r="F119" t="n">
-        <v>-0.00202</v>
+        <v>-0.00356</v>
       </c>
       <c r="G119" t="n">
-        <v>0.29702</v>
+        <v>0.2960200000000001</v>
       </c>
       <c r="H119" t="n">
-        <v>0.68138</v>
+        <v>0.67932</v>
       </c>
       <c r="I119" t="n">
         <v>0.1921</v>
       </c>
       <c r="J119" t="n">
-        <v>0.6437999999999999</v>
+        <v>0.6513199999999999</v>
       </c>
     </row>
     <row r="120">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.268909, "environmental": 0.371359, "comfort": 0.160782, "practicality": 0.19895}</t>
+          <t>{"energy_cost": 0.268683, "environmental": 0.371046, "comfort": 0.16149, "practicality": 0.198782}</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5210,22 +5210,22 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.19794</v>
+        <v>0.19658</v>
       </c>
       <c r="F120" t="n">
-        <v>0.2082</v>
+        <v>0.20872</v>
       </c>
       <c r="G120" t="n">
-        <v>0.4605400000000001</v>
+        <v>0.46462</v>
       </c>
       <c r="H120" t="n">
-        <v>0.75078</v>
+        <v>0.76822</v>
       </c>
       <c r="I120" t="n">
         <v>0.1921</v>
       </c>
       <c r="J120" t="n">
-        <v>0.6437999999999999</v>
+        <v>0.6513199999999999</v>
       </c>
     </row>
     <row r="121">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.268909, "environmental": 0.371359, "comfort": 0.160782, "practicality": 0.19895}</t>
+          <t>{"energy_cost": 0.268683, "environmental": 0.371046, "comfort": 0.16149, "practicality": 0.198782}</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5250,22 +5250,22 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.8417399999999999</v>
+        <v>0.8478999999999999</v>
       </c>
       <c r="F121" t="n">
-        <v>0.85612</v>
+        <v>0.86176</v>
       </c>
       <c r="G121" t="n">
-        <v>0.8756400000000001</v>
+        <v>0.88386</v>
       </c>
       <c r="H121" t="n">
-        <v>0.96402</v>
+        <v>0.9650399999999999</v>
       </c>
       <c r="I121" t="n">
         <v>0.1921</v>
       </c>
       <c r="J121" t="n">
-        <v>0.6437999999999999</v>
+        <v>0.6513199999999999</v>
       </c>
     </row>
     <row r="122">
@@ -5290,22 +5290,22 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.02782</v>
+        <v>0.0257</v>
       </c>
       <c r="F122" t="n">
-        <v>0.0247</v>
+        <v>0.02216</v>
       </c>
       <c r="G122" t="n">
-        <v>0.3217</v>
+        <v>0.3186599999999999</v>
       </c>
       <c r="H122" t="n">
-        <v>0.6916800000000001</v>
+        <v>0.6896</v>
       </c>
       <c r="I122" t="n">
-        <v>0.19408</v>
+        <v>0.19414</v>
       </c>
       <c r="J122" t="n">
-        <v>0.6465800000000002</v>
+        <v>0.6445000000000001</v>
       </c>
     </row>
     <row r="123">
@@ -5330,22 +5330,22 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.2219</v>
+        <v>0.21984</v>
       </c>
       <c r="F123" t="n">
-        <v>0.24</v>
+        <v>0.24206</v>
       </c>
       <c r="G123" t="n">
-        <v>0.4656399999999999</v>
+        <v>0.4584400000000001</v>
       </c>
       <c r="H123" t="n">
-        <v>0.78254</v>
+        <v>0.78874</v>
       </c>
       <c r="I123" t="n">
-        <v>0.19408</v>
+        <v>0.19414</v>
       </c>
       <c r="J123" t="n">
-        <v>0.6465800000000002</v>
+        <v>0.6445000000000001</v>
       </c>
     </row>
     <row r="124">
@@ -5370,22 +5370,22 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.8684800000000001</v>
+        <v>0.86434</v>
       </c>
       <c r="F124" t="n">
-        <v>0.88182</v>
+        <v>0.87822</v>
       </c>
       <c r="G124" t="n">
-        <v>0.8982999999999999</v>
+        <v>0.89312</v>
       </c>
       <c r="H124" t="n">
-        <v>0.9722799999999999</v>
+        <v>0.9712400000000001</v>
       </c>
       <c r="I124" t="n">
-        <v>0.19408</v>
+        <v>0.19414</v>
       </c>
       <c r="J124" t="n">
-        <v>0.6465800000000002</v>
+        <v>0.6445000000000001</v>
       </c>
     </row>
     <row r="125">
@@ -5410,22 +5410,22 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>-0.00988</v>
+        <v>-0.01194</v>
       </c>
       <c r="F125" t="n">
-        <v>-0.01642</v>
+        <v>-0.01794</v>
       </c>
       <c r="G125" t="n">
-        <v>0.296</v>
+        <v>0.29292</v>
       </c>
       <c r="H125" t="n">
         <v>0.6762400000000001</v>
       </c>
       <c r="I125" t="n">
-        <v>0.20918</v>
+        <v>0.20166</v>
       </c>
       <c r="J125" t="n">
-        <v>0.6417599999999999</v>
+        <v>0.6492800000000001</v>
       </c>
     </row>
     <row r="126">
@@ -5450,22 +5450,22 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.1993</v>
+        <v>0.18972</v>
       </c>
       <c r="F126" t="n">
-        <v>0.20718</v>
+        <v>0.19896</v>
       </c>
       <c r="G126" t="n">
-        <v>0.45746</v>
+        <v>0.45642</v>
       </c>
       <c r="H126" t="n">
-        <v>0.76102</v>
+        <v>0.76718</v>
       </c>
       <c r="I126" t="n">
-        <v>0.20918</v>
+        <v>0.20166</v>
       </c>
       <c r="J126" t="n">
-        <v>0.6417599999999999</v>
+        <v>0.6492800000000001</v>
       </c>
     </row>
     <row r="127">
@@ -5490,22 +5490,22 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.8410599999999999</v>
+        <v>0.8390000000000001</v>
       </c>
       <c r="F127" t="n">
-        <v>0.86076</v>
+        <v>0.8592000000000001</v>
       </c>
       <c r="G127" t="n">
-        <v>0.8797599999999999</v>
+        <v>0.8756600000000001</v>
       </c>
       <c r="H127" t="n">
-        <v>0.97432</v>
+        <v>0.9753399999999999</v>
       </c>
       <c r="I127" t="n">
-        <v>0.20918</v>
+        <v>0.20166</v>
       </c>
       <c r="J127" t="n">
-        <v>0.6417599999999999</v>
+        <v>0.6492800000000001</v>
       </c>
     </row>
     <row r="128">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}</t>
+          <t>{"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -5530,22 +5530,22 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.02782</v>
+        <v>0.0237</v>
       </c>
       <c r="F128" t="n">
-        <v>0.0273</v>
+        <v>0.02214</v>
       </c>
       <c r="G128" t="n">
-        <v>0.30628</v>
+        <v>0.30218</v>
       </c>
       <c r="H128" t="n">
-        <v>0.68138</v>
+        <v>0.6793</v>
       </c>
       <c r="I128" t="n">
-        <v>0.14008</v>
+        <v>0.1592</v>
       </c>
       <c r="J128" t="n">
-        <v>0.6409199999999998</v>
+        <v>0.6293800000000001</v>
       </c>
     </row>
     <row r="129">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}</t>
+          <t>{"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -5570,22 +5570,22 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.1679</v>
+        <v>0.1829</v>
       </c>
       <c r="F129" t="n">
-        <v>0.17694</v>
+        <v>0.19334</v>
       </c>
       <c r="G129" t="n">
-        <v>0.45128</v>
+        <v>0.46154</v>
       </c>
       <c r="H129" t="n">
-        <v>0.7425600000000001</v>
+        <v>0.7733399999999999</v>
       </c>
       <c r="I129" t="n">
-        <v>0.14008</v>
+        <v>0.1592</v>
       </c>
       <c r="J129" t="n">
-        <v>0.6409199999999998</v>
+        <v>0.6293800000000001</v>
       </c>
     </row>
     <row r="130">
@@ -5601,7 +5601,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}</t>
+          <t>{"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -5610,22 +5610,22 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.8088199999999999</v>
+        <v>0.8122800000000001</v>
       </c>
       <c r="F130" t="n">
-        <v>0.82786</v>
+        <v>0.83044</v>
       </c>
       <c r="G130" t="n">
-        <v>0.8386400000000001</v>
+        <v>0.8366199999999999</v>
       </c>
       <c r="H130" t="n">
-        <v>0.9619799999999999</v>
+        <v>0.96302</v>
       </c>
       <c r="I130" t="n">
-        <v>0.14008</v>
+        <v>0.1592</v>
       </c>
       <c r="J130" t="n">
-        <v>0.6409199999999998</v>
+        <v>0.6293800000000001</v>
       </c>
     </row>
     <row r="131">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}}</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -5650,22 +5650,22 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>-0.005100000000000001</v>
+        <v>-0.006460000000000002</v>
       </c>
       <c r="F131" t="n">
-        <v>-0.0164</v>
+        <v>-0.01796</v>
       </c>
       <c r="G131" t="n">
-        <v>0.30426</v>
+        <v>0.30324</v>
       </c>
       <c r="H131" t="n">
-        <v>0.6813800000000001</v>
+        <v>0.6793199999999999</v>
       </c>
       <c r="I131" t="n">
-        <v>0.21946</v>
+        <v>0.2263</v>
       </c>
       <c r="J131" t="n">
-        <v>0.67328</v>
+        <v>0.66916</v>
       </c>
     </row>
     <row r="132">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}}</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -5690,22 +5690,22 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.21436</v>
+        <v>0.21984</v>
       </c>
       <c r="F132" t="n">
-        <v>0.2292</v>
+        <v>0.23642</v>
       </c>
       <c r="G132" t="n">
-        <v>0.4554</v>
+        <v>0.46258</v>
       </c>
       <c r="H132" t="n">
-        <v>0.76102</v>
+        <v>0.78462</v>
       </c>
       <c r="I132" t="n">
-        <v>0.21946</v>
+        <v>0.2263</v>
       </c>
       <c r="J132" t="n">
-        <v>0.67328</v>
+        <v>0.66916</v>
       </c>
     </row>
     <row r="133">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}}</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -5730,22 +5730,22 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.88764</v>
+        <v>0.889</v>
       </c>
       <c r="F133" t="n">
-        <v>0.9013200000000001</v>
+        <v>0.90234</v>
       </c>
       <c r="G133" t="n">
-        <v>0.9311400000000001</v>
+        <v>0.93216</v>
       </c>
       <c r="H133" t="n">
-        <v>0.98254</v>
+        <v>0.98356</v>
       </c>
       <c r="I133" t="n">
-        <v>0.21946</v>
+        <v>0.2263</v>
       </c>
       <c r="J133" t="n">
-        <v>0.67328</v>
+        <v>0.66916</v>
       </c>
     </row>
     <row r="134">
@@ -5782,10 +5782,10 @@
         <v>0.67728</v>
       </c>
       <c r="I134" t="n">
-        <v>0.21874</v>
+        <v>0.2201</v>
       </c>
       <c r="J134" t="n">
-        <v>0.69796</v>
+        <v>0.6966000000000001</v>
       </c>
     </row>
     <row r="135">
@@ -5810,22 +5810,22 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0.22396</v>
+        <v>0.22532</v>
       </c>
       <c r="F135" t="n">
-        <v>0.23896</v>
+        <v>0.24102</v>
       </c>
       <c r="G135" t="n">
-        <v>0.48818</v>
+        <v>0.4841</v>
       </c>
       <c r="H135" t="n">
-        <v>0.7723</v>
+        <v>0.7846</v>
       </c>
       <c r="I135" t="n">
-        <v>0.21874</v>
+        <v>0.2201</v>
       </c>
       <c r="J135" t="n">
-        <v>0.69796</v>
+        <v>0.6966000000000001</v>
       </c>
     </row>
     <row r="136">
@@ -5862,10 +5862,10 @@
         <v>0.97944</v>
       </c>
       <c r="I136" t="n">
-        <v>0.21874</v>
+        <v>0.2201</v>
       </c>
       <c r="J136" t="n">
-        <v>0.69796</v>
+        <v>0.6966000000000001</v>
       </c>
     </row>
     <row r="137">
@@ -5902,10 +5902,10 @@
         <v>0.6978</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1886</v>
+        <v>0.18994</v>
       </c>
       <c r="J137" t="n">
-        <v>0.64392</v>
+        <v>0.64258</v>
       </c>
     </row>
     <row r="138">
@@ -5930,22 +5930,22 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.25952</v>
+        <v>0.26086</v>
       </c>
       <c r="F138" t="n">
-        <v>0.27744</v>
+        <v>0.2794800000000001</v>
       </c>
       <c r="G138" t="n">
-        <v>0.49642</v>
+        <v>0.4922800000000001</v>
       </c>
       <c r="H138" t="n">
-        <v>0.76512</v>
+        <v>0.7774599999999999</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1886</v>
+        <v>0.18994</v>
       </c>
       <c r="J138" t="n">
-        <v>0.64392</v>
+        <v>0.64258</v>
       </c>
     </row>
     <row r="139">
@@ -5982,10 +5982,10 @@
         <v>0.97536</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1886</v>
+        <v>0.18994</v>
       </c>
       <c r="J139" t="n">
-        <v>0.64392</v>
+        <v>0.64258</v>
       </c>
     </row>
     <row r="140">
@@ -6022,10 +6022,10 @@
         <v>0.65778</v>
       </c>
       <c r="I140" t="n">
-        <v>0.21398</v>
+        <v>0.18734</v>
       </c>
       <c r="J140" t="n">
-        <v>0.6629999999999999</v>
+        <v>0.68554</v>
       </c>
     </row>
     <row r="141">
@@ -6050,22 +6050,22 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.19794</v>
+        <v>0.1713</v>
       </c>
       <c r="F141" t="n">
-        <v>0.21436</v>
+        <v>0.18616</v>
       </c>
       <c r="G141" t="n">
-        <v>0.4636</v>
+        <v>0.45026</v>
       </c>
       <c r="H141" t="n">
-        <v>0.7723000000000001</v>
+        <v>0.7712600000000001</v>
       </c>
       <c r="I141" t="n">
-        <v>0.21398</v>
+        <v>0.18734</v>
       </c>
       <c r="J141" t="n">
-        <v>0.6629999999999999</v>
+        <v>0.68554</v>
       </c>
     </row>
     <row r="142">
@@ -6090,22 +6090,22 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.8609399999999999</v>
+        <v>0.85684</v>
       </c>
       <c r="F142" t="n">
-        <v>0.87514</v>
+        <v>0.87102</v>
       </c>
       <c r="G142" t="n">
-        <v>0.8633200000000001</v>
+        <v>0.86126</v>
       </c>
       <c r="H142" t="n">
         <v>0.97226</v>
       </c>
       <c r="I142" t="n">
-        <v>0.21398</v>
+        <v>0.18734</v>
       </c>
       <c r="J142" t="n">
-        <v>0.6629999999999999</v>
+        <v>0.68554</v>
       </c>
     </row>
     <row r="143">
@@ -6130,22 +6130,22 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>-0.005100000000000001</v>
+        <v>-0.007179999999999997</v>
       </c>
       <c r="F143" t="n">
-        <v>-0.0164</v>
+        <v>-0.01796</v>
       </c>
       <c r="G143" t="n">
-        <v>0.30426</v>
+        <v>0.30116</v>
       </c>
       <c r="H143" t="n">
-        <v>0.6813800000000001</v>
+        <v>0.68136</v>
       </c>
       <c r="I143" t="n">
-        <v>0.22014</v>
+        <v>0.22564</v>
       </c>
       <c r="J143" t="n">
-        <v>0.6726</v>
+        <v>0.66712</v>
       </c>
     </row>
     <row r="144">
@@ -6170,22 +6170,22 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.21504</v>
+        <v>0.21846</v>
       </c>
       <c r="F144" t="n">
-        <v>0.23026</v>
+        <v>0.23538</v>
       </c>
       <c r="G144" t="n">
-        <v>0.45438</v>
+        <v>0.4605399999999999</v>
       </c>
       <c r="H144" t="n">
-        <v>0.7630800000000001</v>
+        <v>0.7846200000000001</v>
       </c>
       <c r="I144" t="n">
-        <v>0.22014</v>
+        <v>0.22564</v>
       </c>
       <c r="J144" t="n">
-        <v>0.6726</v>
+        <v>0.66712</v>
       </c>
     </row>
     <row r="145">
@@ -6210,22 +6210,22 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0.88764</v>
+        <v>0.88558</v>
       </c>
       <c r="F145" t="n">
-        <v>0.9013200000000001</v>
+        <v>0.89984</v>
       </c>
       <c r="G145" t="n">
-        <v>0.9311400000000001</v>
+        <v>0.9270400000000001</v>
       </c>
       <c r="H145" t="n">
-        <v>0.98254</v>
+        <v>0.98356</v>
       </c>
       <c r="I145" t="n">
-        <v>0.22014</v>
+        <v>0.22564</v>
       </c>
       <c r="J145" t="n">
-        <v>0.6726</v>
+        <v>0.66712</v>
       </c>
     </row>
     <row r="146">
@@ -6262,10 +6262,10 @@
         <v>0.7221</v>
       </c>
       <c r="I146" t="n">
-        <v>0.18386</v>
+        <v>0.16268</v>
       </c>
       <c r="J146" t="n">
-        <v>0.56948</v>
+        <v>0.5906400000000001</v>
       </c>
     </row>
     <row r="147">
@@ -6290,22 +6290,22 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.32786</v>
+        <v>0.30668</v>
       </c>
       <c r="F147" t="n">
-        <v>0.35384</v>
+        <v>0.33078</v>
       </c>
       <c r="G147" t="n">
-        <v>0.5446</v>
+        <v>0.5353800000000001</v>
       </c>
       <c r="H147" t="n">
-        <v>0.8154</v>
+        <v>0.8112999999999999</v>
       </c>
       <c r="I147" t="n">
-        <v>0.18386</v>
+        <v>0.16268</v>
       </c>
       <c r="J147" t="n">
-        <v>0.56948</v>
+        <v>0.5906400000000001</v>
       </c>
     </row>
     <row r="148">
@@ -6330,22 +6330,22 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0.89734</v>
+        <v>0.89732</v>
       </c>
       <c r="F148" t="n">
         <v>0.9101399999999999</v>
       </c>
       <c r="G148" t="n">
-        <v>0.90762</v>
+        <v>0.9076000000000001</v>
       </c>
       <c r="H148" t="n">
         <v>0.9774200000000001</v>
       </c>
       <c r="I148" t="n">
-        <v>0.18386</v>
+        <v>0.16268</v>
       </c>
       <c r="J148" t="n">
-        <v>0.56948</v>
+        <v>0.5906400000000001</v>
       </c>
     </row>
     <row r="149">
@@ -6370,22 +6370,22 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.20258</v>
+        <v>0.20048</v>
       </c>
       <c r="F149" t="n">
-        <v>0.20982</v>
+        <v>0.20774</v>
       </c>
       <c r="G149" t="n">
-        <v>0.4091799999999999</v>
+        <v>0.4061</v>
       </c>
       <c r="H149" t="n">
-        <v>0.7531199999999999</v>
+        <v>0.75208</v>
       </c>
       <c r="I149" t="n">
-        <v>0.13346</v>
+        <v>0.10894</v>
       </c>
       <c r="J149" t="n">
-        <v>0.54144</v>
+        <v>0.57216</v>
       </c>
     </row>
     <row r="150">
@@ -6410,22 +6410,22 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.33604</v>
+        <v>0.30942</v>
       </c>
       <c r="F150" t="n">
-        <v>0.35692</v>
+        <v>0.32924</v>
       </c>
       <c r="G150" t="n">
-        <v>0.5497400000000001</v>
+        <v>0.5364</v>
       </c>
       <c r="H150" t="n">
-        <v>0.8194800000000001</v>
+        <v>0.8184799999999999</v>
       </c>
       <c r="I150" t="n">
-        <v>0.13346</v>
+        <v>0.10894</v>
       </c>
       <c r="J150" t="n">
-        <v>0.54144</v>
+        <v>0.57216</v>
       </c>
     </row>
     <row r="151">
@@ -6450,22 +6450,22 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.87748</v>
+        <v>0.8815799999999999</v>
       </c>
       <c r="F151" t="n">
-        <v>0.8947799999999999</v>
+        <v>0.8978200000000001</v>
       </c>
       <c r="G151" t="n">
-        <v>0.8942399999999999</v>
+        <v>0.9004200000000001</v>
       </c>
       <c r="H151" t="n">
         <v>0.9784600000000001</v>
       </c>
       <c r="I151" t="n">
-        <v>0.13346</v>
+        <v>0.10894</v>
       </c>
       <c r="J151" t="n">
-        <v>0.54144</v>
+        <v>0.57216</v>
       </c>
     </row>
     <row r="152">
@@ -6490,10 +6490,10 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0.12056</v>
+        <v>0.11852</v>
       </c>
       <c r="F152" t="n">
-        <v>0.12146</v>
+        <v>0.11886</v>
       </c>
       <c r="G152" t="n">
         <v>0.3565</v>
@@ -6502,10 +6502,10 @@
         <v>0.71696</v>
       </c>
       <c r="I152" t="n">
-        <v>0.21824</v>
+        <v>0.19772</v>
       </c>
       <c r="J152" t="n">
-        <v>0.5763</v>
+        <v>0.6016</v>
       </c>
     </row>
     <row r="153">
@@ -6530,22 +6530,22 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>0.3388</v>
+        <v>0.31624</v>
       </c>
       <c r="F153" t="n">
-        <v>0.36922</v>
+        <v>0.34562</v>
       </c>
       <c r="G153" t="n">
-        <v>0.5374399999999999</v>
+        <v>0.5364</v>
       </c>
       <c r="H153" t="n">
-        <v>0.8389800000000001</v>
+        <v>0.8266600000000001</v>
       </c>
       <c r="I153" t="n">
-        <v>0.21824</v>
+        <v>0.19772</v>
       </c>
       <c r="J153" t="n">
-        <v>0.5763</v>
+        <v>0.6016</v>
       </c>
     </row>
     <row r="154">
@@ -6570,22 +6570,22 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.9151</v>
+        <v>0.91784</v>
       </c>
       <c r="F154" t="n">
-        <v>0.9281200000000001</v>
+        <v>0.92968</v>
       </c>
       <c r="G154" t="n">
-        <v>0.9301600000000001</v>
+        <v>0.9343</v>
       </c>
       <c r="H154" t="n">
-        <v>0.9907599999999999</v>
+        <v>0.99178</v>
       </c>
       <c r="I154" t="n">
-        <v>0.21824</v>
+        <v>0.19772</v>
       </c>
       <c r="J154" t="n">
-        <v>0.5763</v>
+        <v>0.6016</v>
       </c>
     </row>
     <row r="155">
@@ -6610,22 +6610,22 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.17502</v>
+        <v>0.1695</v>
       </c>
       <c r="F155" t="n">
-        <v>0.17832</v>
+        <v>0.1721</v>
       </c>
       <c r="G155" t="n">
-        <v>0.3813</v>
+        <v>0.37818</v>
       </c>
       <c r="H155" t="n">
-        <v>0.73454</v>
+        <v>0.7334999999999999</v>
       </c>
       <c r="I155" t="n">
-        <v>0.16788</v>
+        <v>0.1460599999999999</v>
       </c>
       <c r="J155" t="n">
-        <v>0.54416</v>
+        <v>0.5694400000000001</v>
       </c>
     </row>
     <row r="156">
@@ -6650,22 +6650,22 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0.3429</v>
+        <v>0.31556</v>
       </c>
       <c r="F156" t="n">
-        <v>0.3672000000000001</v>
+        <v>0.33742</v>
       </c>
       <c r="G156" t="n">
-        <v>0.5599999999999999</v>
+        <v>0.5487400000000001</v>
       </c>
       <c r="H156" t="n">
-        <v>0.8215199999999999</v>
+        <v>0.8205200000000001</v>
       </c>
       <c r="I156" t="n">
-        <v>0.16788</v>
+        <v>0.1460599999999999</v>
       </c>
       <c r="J156" t="n">
-        <v>0.54416</v>
+        <v>0.5694400000000001</v>
       </c>
     </row>
     <row r="157">
@@ -6690,22 +6690,22 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.88706</v>
+        <v>0.885</v>
       </c>
       <c r="F157" t="n">
-        <v>0.90452</v>
+        <v>0.9014200000000001</v>
       </c>
       <c r="G157" t="n">
-        <v>0.8942600000000001</v>
+        <v>0.8994</v>
       </c>
       <c r="H157" t="n">
-        <v>0.9784600000000001</v>
+        <v>0.9753400000000001</v>
       </c>
       <c r="I157" t="n">
-        <v>0.16788</v>
+        <v>0.1460599999999999</v>
       </c>
       <c r="J157" t="n">
-        <v>0.54416</v>
+        <v>0.5694400000000001</v>
       </c>
     </row>
     <row r="158">
@@ -6742,10 +6742,10 @@
         <v>0.71594</v>
       </c>
       <c r="I158" t="n">
-        <v>0.19694</v>
+        <v>0.1819199999999999</v>
       </c>
       <c r="J158" t="n">
-        <v>0.5947999999999999</v>
+        <v>0.61322</v>
       </c>
     </row>
     <row r="159">
@@ -6770,22 +6770,22 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.3217</v>
+        <v>0.30668</v>
       </c>
       <c r="F159" t="n">
-        <v>0.3518</v>
+        <v>0.33538</v>
       </c>
       <c r="G159" t="n">
-        <v>0.52718</v>
+        <v>0.5282</v>
       </c>
       <c r="H159" t="n">
-        <v>0.8369399999999999</v>
+        <v>0.8245999999999999</v>
       </c>
       <c r="I159" t="n">
-        <v>0.19694</v>
+        <v>0.1819199999999999</v>
       </c>
       <c r="J159" t="n">
-        <v>0.5947999999999999</v>
+        <v>0.61322</v>
       </c>
     </row>
     <row r="160">
@@ -6810,22 +6810,22 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0.9164999999999999</v>
+        <v>0.9198999999999999</v>
       </c>
       <c r="F160" t="n">
-        <v>0.92864</v>
+        <v>0.9311999999999999</v>
       </c>
       <c r="G160" t="n">
-        <v>0.93122</v>
+        <v>0.9353199999999999</v>
       </c>
       <c r="H160" t="n">
-        <v>0.9907599999999999</v>
+        <v>0.99178</v>
       </c>
       <c r="I160" t="n">
-        <v>0.19694</v>
+        <v>0.1819199999999999</v>
       </c>
       <c r="J160" t="n">
-        <v>0.5947999999999999</v>
+        <v>0.61322</v>
       </c>
     </row>
     <row r="161">
@@ -6850,22 +6850,22 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>0.1144</v>
+        <v>0.11304</v>
       </c>
       <c r="F161" t="n">
-        <v>0.11582</v>
+        <v>0.11374</v>
       </c>
       <c r="G161" t="n">
         <v>0.35546</v>
       </c>
       <c r="H161" t="n">
-        <v>0.7149799999999999</v>
+        <v>0.71494</v>
       </c>
       <c r="I161" t="n">
-        <v>0.20662</v>
+        <v>0.1929600000000001</v>
       </c>
       <c r="J161" t="n">
-        <v>0.5879400000000001</v>
+        <v>0.6063799999999999</v>
       </c>
     </row>
     <row r="162">
@@ -6890,22 +6890,22 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>0.32102</v>
+        <v>0.306</v>
       </c>
       <c r="F162" t="n">
-        <v>0.35538</v>
+        <v>0.33796</v>
       </c>
       <c r="G162" t="n">
-        <v>0.5312800000000001</v>
+        <v>0.5313</v>
       </c>
       <c r="H162" t="n">
-        <v>0.8338599999999999</v>
+        <v>0.8266600000000001</v>
       </c>
       <c r="I162" t="n">
-        <v>0.20662</v>
+        <v>0.1929600000000001</v>
       </c>
       <c r="J162" t="n">
-        <v>0.5879400000000001</v>
+        <v>0.6063799999999999</v>
       </c>
     </row>
     <row r="163">
@@ -6930,22 +6930,22 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.9089600000000001</v>
+        <v>0.91238</v>
       </c>
       <c r="F163" t="n">
-        <v>0.9214399999999999</v>
+        <v>0.9224599999999998</v>
       </c>
       <c r="G163" t="n">
-        <v>0.9209400000000001</v>
+        <v>0.92606</v>
       </c>
       <c r="H163" t="n">
-        <v>0.9866200000000001</v>
+        <v>0.9856199999999999</v>
       </c>
       <c r="I163" t="n">
-        <v>0.20662</v>
+        <v>0.1929600000000001</v>
       </c>
       <c r="J163" t="n">
-        <v>0.5879400000000001</v>
+        <v>0.6063799999999999</v>
       </c>
     </row>
     <row r="164">
@@ -6970,22 +6970,22 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>0.19906</v>
+        <v>0.19564</v>
       </c>
       <c r="F164" t="n">
-        <v>0.20664</v>
+        <v>0.20354</v>
       </c>
       <c r="G164" t="n">
-        <v>0.39672</v>
+        <v>0.39158</v>
       </c>
       <c r="H164" t="n">
-        <v>0.7448599999999999</v>
+        <v>0.7438199999999999</v>
       </c>
       <c r="I164" t="n">
-        <v>0.14248</v>
+        <v>0.1206</v>
       </c>
       <c r="J164" t="n">
-        <v>0.5235999999999998</v>
+        <v>0.5496000000000001</v>
       </c>
     </row>
     <row r="165">
@@ -7010,22 +7010,22 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.34154</v>
+        <v>0.31624</v>
       </c>
       <c r="F165" t="n">
-        <v>0.3595</v>
+        <v>0.33488</v>
       </c>
       <c r="G165" t="n">
-        <v>0.55794</v>
+        <v>0.5466599999999999</v>
       </c>
       <c r="H165" t="n">
-        <v>0.82256</v>
+        <v>0.8174400000000001</v>
       </c>
       <c r="I165" t="n">
-        <v>0.14248</v>
+        <v>0.1206</v>
       </c>
       <c r="J165" t="n">
-        <v>0.5235999999999998</v>
+        <v>0.5496000000000001</v>
       </c>
     </row>
     <row r="166">
@@ -7050,22 +7050,22 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.8651399999999999</v>
+        <v>0.8658400000000001</v>
       </c>
       <c r="F166" t="n">
-        <v>0.88192</v>
+        <v>0.8809000000000001</v>
       </c>
       <c r="G166" t="n">
-        <v>0.8963000000000001</v>
+        <v>0.9004199999999999</v>
       </c>
       <c r="H166" t="n">
-        <v>0.9712400000000001</v>
+        <v>0.96818</v>
       </c>
       <c r="I166" t="n">
-        <v>0.14248</v>
+        <v>0.1206</v>
       </c>
       <c r="J166" t="n">
-        <v>0.5235999999999998</v>
+        <v>0.5496000000000001</v>
       </c>
     </row>
     <row r="167">
@@ -7090,10 +7090,10 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0.11786</v>
+        <v>0.11442</v>
       </c>
       <c r="F167" t="n">
-        <v>0.12046</v>
+        <v>0.11688</v>
       </c>
       <c r="G167" t="n">
         <v>0.34826</v>
@@ -7102,10 +7102,10 @@
         <v>0.7179800000000001</v>
       </c>
       <c r="I167" t="n">
-        <v>0.1929</v>
+        <v>0.1779</v>
       </c>
       <c r="J167" t="n">
-        <v>0.59272</v>
+        <v>0.6173199999999999</v>
       </c>
     </row>
     <row r="168">
@@ -7130,22 +7130,22 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0.31076</v>
+        <v>0.29232</v>
       </c>
       <c r="F168" t="n">
-        <v>0.33384</v>
+        <v>0.31232</v>
       </c>
       <c r="G168" t="n">
-        <v>0.5210399999999999</v>
+        <v>0.52102</v>
       </c>
       <c r="H168" t="n">
-        <v>0.8164200000000001</v>
+        <v>0.8</v>
       </c>
       <c r="I168" t="n">
-        <v>0.1929</v>
+        <v>0.1779</v>
       </c>
       <c r="J168" t="n">
-        <v>0.59272</v>
+        <v>0.6173199999999999</v>
       </c>
     </row>
     <row r="169">
@@ -7170,22 +7170,22 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0.9034800000000001</v>
+        <v>0.9096399999999999</v>
       </c>
       <c r="F169" t="n">
-        <v>0.9193999999999999</v>
+        <v>0.9266</v>
       </c>
       <c r="G169" t="n">
-        <v>0.9168200000000001</v>
+        <v>0.9198999999999999</v>
       </c>
       <c r="H169" t="n">
-        <v>0.99178</v>
+        <v>0.99074</v>
       </c>
       <c r="I169" t="n">
-        <v>0.1929</v>
+        <v>0.1779</v>
       </c>
       <c r="J169" t="n">
-        <v>0.59272</v>
+        <v>0.6173199999999999</v>
       </c>
     </row>
     <row r="170">
@@ -7210,10 +7210,10 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>0.1833</v>
+        <v>0.17984</v>
       </c>
       <c r="F170" t="n">
-        <v>0.18866</v>
+        <v>0.18452</v>
       </c>
       <c r="G170" t="n">
         <v>0.39266</v>
@@ -7222,10 +7222,10 @@
         <v>0.74282</v>
       </c>
       <c r="I170" t="n">
-        <v>0.16164</v>
+        <v>0.13502</v>
       </c>
       <c r="J170" t="n">
-        <v>0.5537400000000001</v>
+        <v>0.5804</v>
       </c>
     </row>
     <row r="171">
@@ -7250,22 +7250,22 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>0.34494</v>
+        <v>0.31486</v>
       </c>
       <c r="F171" t="n">
-        <v>0.36668</v>
+        <v>0.3369</v>
       </c>
       <c r="G171" t="n">
-        <v>0.55076</v>
+        <v>0.5395</v>
       </c>
       <c r="H171" t="n">
-        <v>0.8215600000000001</v>
+        <v>0.82154</v>
       </c>
       <c r="I171" t="n">
-        <v>0.16164</v>
+        <v>0.13502</v>
       </c>
       <c r="J171" t="n">
-        <v>0.5537400000000001</v>
+        <v>0.5804</v>
       </c>
     </row>
     <row r="172">
@@ -7290,10 +7290,10 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>0.89868</v>
+        <v>0.8952600000000001</v>
       </c>
       <c r="F172" t="n">
-        <v>0.91478</v>
+        <v>0.9122</v>
       </c>
       <c r="G172" t="n">
         <v>0.90862</v>
@@ -7302,10 +7302,10 @@
         <v>0.98256</v>
       </c>
       <c r="I172" t="n">
-        <v>0.16164</v>
+        <v>0.13502</v>
       </c>
       <c r="J172" t="n">
-        <v>0.5537400000000001</v>
+        <v>0.5804</v>
       </c>
     </row>
     <row r="173">
@@ -7330,10 +7330,10 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>0.11302</v>
+        <v>0.11508</v>
       </c>
       <c r="F173" t="n">
-        <v>0.11686</v>
+        <v>0.1189</v>
       </c>
       <c r="G173" t="n">
         <v>0.3679</v>
@@ -7342,10 +7342,10 @@
         <v>0.7231799999999999</v>
       </c>
       <c r="I173" t="n">
-        <v>0.20322</v>
+        <v>0.19636</v>
       </c>
       <c r="J173" t="n">
-        <v>0.5975</v>
+        <v>0.5975200000000001</v>
       </c>
     </row>
     <row r="174">
@@ -7370,22 +7370,22 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>0.31624</v>
+        <v>0.31144</v>
       </c>
       <c r="F174" t="n">
-        <v>0.3446</v>
+        <v>0.3323</v>
       </c>
       <c r="G174" t="n">
-        <v>0.5220399999999999</v>
+        <v>0.52512</v>
       </c>
       <c r="H174" t="n">
-        <v>0.82872</v>
+        <v>0.8195</v>
       </c>
       <c r="I174" t="n">
-        <v>0.20322</v>
+        <v>0.19636</v>
       </c>
       <c r="J174" t="n">
-        <v>0.5975</v>
+        <v>0.5975200000000001</v>
       </c>
     </row>
     <row r="175">
@@ -7410,10 +7410,10 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>0.91374</v>
+        <v>0.9089600000000001</v>
       </c>
       <c r="F175" t="n">
-        <v>0.9301600000000001</v>
+        <v>0.9265800000000001</v>
       </c>
       <c r="G175" t="n">
         <v>0.9373400000000001</v>
@@ -7422,10 +7422,10 @@
         <v>0.99382</v>
       </c>
       <c r="I175" t="n">
-        <v>0.20322</v>
+        <v>0.19636</v>
       </c>
       <c r="J175" t="n">
-        <v>0.5975</v>
+        <v>0.5975200000000001</v>
       </c>
     </row>
     <row r="176">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.194172, "environmental": 0.131673, "comfort": 0.401912, "practicality": 0.272243}</t>
+          <t>{"energy_cost": 0.1943, "environmental": 0.131354, "comfort": 0.403745, "practicality": 0.2706}</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -7450,22 +7450,22 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>0.21884</v>
+        <v>0.22022</v>
       </c>
       <c r="F176" t="n">
-        <v>0.24516</v>
+        <v>0.24618</v>
       </c>
       <c r="G176" t="n">
-        <v>0.4347800000000001</v>
+        <v>0.43582</v>
       </c>
       <c r="H176" t="n">
         <v>0.7757400000000001</v>
       </c>
       <c r="I176" t="n">
-        <v>0.20954</v>
+        <v>0.1897</v>
       </c>
       <c r="J176" t="n">
-        <v>0.51616</v>
+        <v>0.5531</v>
       </c>
     </row>
     <row r="177">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.194172, "environmental": 0.131673, "comfort": 0.401912, "practicality": 0.272243}</t>
+          <t>{"energy_cost": 0.1943, "environmental": 0.131354, "comfort": 0.403745, "practicality": 0.2706}</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -7490,22 +7490,22 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>0.42838</v>
+        <v>0.40992</v>
       </c>
       <c r="F177" t="n">
-        <v>0.46258</v>
+        <v>0.44204</v>
       </c>
       <c r="G177" t="n">
-        <v>0.5825600000000001</v>
+        <v>0.57436</v>
       </c>
       <c r="H177" t="n">
-        <v>0.8656200000000001</v>
+        <v>0.8615600000000001</v>
       </c>
       <c r="I177" t="n">
-        <v>0.20954</v>
+        <v>0.1897</v>
       </c>
       <c r="J177" t="n">
-        <v>0.51616</v>
+        <v>0.5531</v>
       </c>
     </row>
     <row r="178">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.194172, "environmental": 0.131673, "comfort": 0.401912, "practicality": 0.272243}</t>
+          <t>{"energy_cost": 0.1943, "environmental": 0.131354, "comfort": 0.403745, "practicality": 0.2706}</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -7530,22 +7530,22 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>0.9445399999999999</v>
+        <v>0.96302</v>
       </c>
       <c r="F178" t="n">
-        <v>0.9583999999999999</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="G178" t="n">
-        <v>0.93018</v>
+        <v>0.9547800000000001</v>
       </c>
       <c r="H178" t="n">
         <v>1</v>
       </c>
       <c r="I178" t="n">
-        <v>0.20954</v>
+        <v>0.1897</v>
       </c>
       <c r="J178" t="n">
-        <v>0.51616</v>
+        <v>0.5531</v>
       </c>
     </row>
     <row r="179">
@@ -7582,10 +7582,10 @@
         <v>0.8273999999999999</v>
       </c>
       <c r="I179" t="n">
-        <v>0.10688</v>
+        <v>0.07951999999999998</v>
       </c>
       <c r="J179" t="n">
-        <v>0.5312599999999998</v>
+        <v>0.5716399999999999</v>
       </c>
     </row>
     <row r="180">
@@ -7610,22 +7610,22 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>0.43998</v>
+        <v>0.41262</v>
       </c>
       <c r="F180" t="n">
-        <v>0.4749</v>
+        <v>0.43948</v>
       </c>
       <c r="G180" t="n">
-        <v>0.5815399999999999</v>
+        <v>0.5651400000000001</v>
       </c>
       <c r="H180" t="n">
-        <v>0.8738400000000001</v>
+        <v>0.8646200000000001</v>
       </c>
       <c r="I180" t="n">
-        <v>0.10688</v>
+        <v>0.07951999999999998</v>
       </c>
       <c r="J180" t="n">
-        <v>0.5312599999999998</v>
+        <v>0.5716399999999999</v>
       </c>
     </row>
     <row r="181">
@@ -7650,22 +7650,22 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>0.9712399999999999</v>
+        <v>0.9842599999999999</v>
       </c>
       <c r="F181" t="n">
-        <v>0.97844</v>
+        <v>0.9881800000000001</v>
       </c>
       <c r="G181" t="n">
-        <v>0.961</v>
+        <v>0.97948</v>
       </c>
       <c r="H181" t="n">
         <v>1</v>
       </c>
       <c r="I181" t="n">
-        <v>0.10688</v>
+        <v>0.07951999999999998</v>
       </c>
       <c r="J181" t="n">
-        <v>0.5312599999999998</v>
+        <v>0.5716399999999999</v>
       </c>
     </row>
     <row r="182">
@@ -7702,10 +7702,10 @@
         <v>0.70244</v>
       </c>
       <c r="I182" t="n">
-        <v>0.2640799999999999</v>
+        <v>0.25178</v>
       </c>
       <c r="J182" t="n">
-        <v>0.5188600000000001</v>
+        <v>0.5496799999999999</v>
       </c>
     </row>
     <row r="183">
@@ -7730,22 +7730,22 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>0.4010199999999999</v>
+        <v>0.38872</v>
       </c>
       <c r="F183" t="n">
-        <v>0.42766</v>
+        <v>0.4118000000000001</v>
       </c>
       <c r="G183" t="n">
-        <v>0.5763999999999999</v>
+        <v>0.57026</v>
       </c>
       <c r="H183" t="n">
-        <v>0.85436</v>
+        <v>0.8420400000000001</v>
       </c>
       <c r="I183" t="n">
-        <v>0.2640799999999999</v>
+        <v>0.25178</v>
       </c>
       <c r="J183" t="n">
-        <v>0.5188600000000001</v>
+        <v>0.5496799999999999</v>
       </c>
     </row>
     <row r="184">
@@ -7770,22 +7770,22 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>0.91988</v>
+        <v>0.9384</v>
       </c>
       <c r="F184" t="n">
-        <v>0.93686</v>
+        <v>0.9517599999999999</v>
       </c>
       <c r="G184" t="n">
-        <v>0.9229800000000001</v>
+        <v>0.9281</v>
       </c>
       <c r="H184" t="n">
-        <v>0.99796</v>
+        <v>1</v>
       </c>
       <c r="I184" t="n">
-        <v>0.2640799999999999</v>
+        <v>0.25178</v>
       </c>
       <c r="J184" t="n">
-        <v>0.5188600000000001</v>
+        <v>0.5496799999999999</v>
       </c>
     </row>
     <row r="185">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}</t>
+          <t>{"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -7810,22 +7810,22 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>0.12266</v>
+        <v>0.12332</v>
       </c>
       <c r="F185" t="n">
-        <v>0.13026</v>
+        <v>0.1318</v>
       </c>
       <c r="G185" t="n">
-        <v>0.36066</v>
+        <v>0.36166</v>
       </c>
       <c r="H185" t="n">
-        <v>0.72624</v>
+        <v>0.7231400000000001</v>
       </c>
       <c r="I185" t="n">
-        <v>0.17786</v>
+        <v>0.15054</v>
       </c>
       <c r="J185" t="n">
-        <v>0.5961000000000001</v>
+        <v>0.61866</v>
       </c>
     </row>
     <row r="186">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}</t>
+          <t>{"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -7850,22 +7850,22 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>0.30052</v>
+        <v>0.27386</v>
       </c>
       <c r="F186" t="n">
-        <v>0.32104</v>
+        <v>0.29282</v>
       </c>
       <c r="G186" t="n">
-        <v>0.4995</v>
+        <v>0.4923</v>
       </c>
       <c r="H186" t="n">
-        <v>0.8194800000000001</v>
+        <v>0.8</v>
       </c>
       <c r="I186" t="n">
-        <v>0.17786</v>
+        <v>0.15054</v>
       </c>
       <c r="J186" t="n">
-        <v>0.5961000000000001</v>
+        <v>0.61866</v>
       </c>
     </row>
     <row r="187">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}</t>
+          <t>{"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -7890,22 +7890,22 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>0.8966200000000001</v>
+        <v>0.89252</v>
       </c>
       <c r="F187" t="n">
-        <v>0.9163</v>
+        <v>0.91272</v>
       </c>
       <c r="G187" t="n">
-        <v>0.91478</v>
+        <v>0.9127000000000001</v>
       </c>
       <c r="H187" t="n">
         <v>0.9927800000000001</v>
       </c>
       <c r="I187" t="n">
-        <v>0.17786</v>
+        <v>0.15054</v>
       </c>
       <c r="J187" t="n">
-        <v>0.5961000000000001</v>
+        <v>0.61866</v>
       </c>
     </row>
     <row r="188">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}}</t>
+          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}}</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -7930,22 +7930,22 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>0.30772</v>
+        <v>0.30838</v>
       </c>
       <c r="F188" t="n">
-        <v>0.3299</v>
+        <v>0.33094</v>
       </c>
       <c r="G188" t="n">
-        <v>0.49478</v>
+        <v>0.49374</v>
       </c>
       <c r="H188" t="n">
         <v>0.8108999999999998</v>
       </c>
       <c r="I188" t="n">
-        <v>0.08167999999999997</v>
+        <v>0.05846000000000001</v>
       </c>
       <c r="J188" t="n">
-        <v>0.5414600000000001</v>
+        <v>0.56334</v>
       </c>
     </row>
     <row r="189">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}}</t>
+          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}}</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -7970,22 +7970,22 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>0.3894</v>
+        <v>0.36684</v>
       </c>
       <c r="F189" t="n">
-        <v>0.41434</v>
+        <v>0.38822</v>
       </c>
       <c r="G189" t="n">
-        <v>0.5292199999999999</v>
+        <v>0.5261600000000001</v>
       </c>
       <c r="H189" t="n">
-        <v>0.86668</v>
+        <v>0.84618</v>
       </c>
       <c r="I189" t="n">
-        <v>0.08167999999999997</v>
+        <v>0.05846000000000001</v>
       </c>
       <c r="J189" t="n">
-        <v>0.5414600000000001</v>
+        <v>0.56334</v>
       </c>
     </row>
     <row r="190">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}}</t>
+          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}}</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -8010,22 +8010,22 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>0.93086</v>
+        <v>0.93018</v>
       </c>
       <c r="F190" t="n">
-        <v>0.9424800000000001</v>
+        <v>0.94146</v>
       </c>
       <c r="G190" t="n">
-        <v>0.94148</v>
+        <v>0.9445399999999999</v>
       </c>
       <c r="H190" t="n">
         <v>0.9927800000000001</v>
       </c>
       <c r="I190" t="n">
-        <v>0.08167999999999997</v>
+        <v>0.05846000000000001</v>
       </c>
       <c r="J190" t="n">
-        <v>0.5414600000000001</v>
+        <v>0.56334</v>
       </c>
     </row>
     <row r="191">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.268909, "environmental": 0.371359, "comfort": 0.160782, "practicality": 0.19895}</t>
+          <t>{"energy_cost": 0.268683, "environmental": 0.371046, "comfort": 0.16149, "practicality": 0.198782}</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -8050,22 +8050,22 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>0.1226</v>
+        <v>0.12608</v>
       </c>
       <c r="F191" t="n">
-        <v>0.12814</v>
+        <v>0.13074</v>
       </c>
       <c r="G191" t="n">
-        <v>0.35128</v>
+        <v>0.35544</v>
       </c>
       <c r="H191" t="n">
-        <v>0.71898</v>
+        <v>0.71796</v>
       </c>
       <c r="I191" t="n">
-        <v>0.20118</v>
+        <v>0.1881</v>
       </c>
       <c r="J191" t="n">
-        <v>0.5413600000000001</v>
+        <v>0.5591799999999999</v>
       </c>
     </row>
     <row r="192">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.268909, "environmental": 0.371359, "comfort": 0.160782, "practicality": 0.19895}</t>
+          <t>{"energy_cost": 0.268683, "environmental": 0.371046, "comfort": 0.16149, "practicality": 0.198782}</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -8090,22 +8090,22 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>0.32378</v>
+        <v>0.31418</v>
       </c>
       <c r="F192" t="n">
-        <v>0.34258</v>
+        <v>0.3323</v>
       </c>
       <c r="G192" t="n">
-        <v>0.5323399999999999</v>
+        <v>0.5415399999999999</v>
       </c>
       <c r="H192" t="n">
-        <v>0.8112999999999999</v>
+        <v>0.80514</v>
       </c>
       <c r="I192" t="n">
-        <v>0.20118</v>
+        <v>0.1881</v>
       </c>
       <c r="J192" t="n">
-        <v>0.5413600000000001</v>
+        <v>0.5591799999999999</v>
       </c>
     </row>
     <row r="193">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.268909, "environmental": 0.371359, "comfort": 0.160782, "practicality": 0.19895}</t>
+          <t>{"energy_cost": 0.268683, "environmental": 0.371046, "comfort": 0.16149, "practicality": 0.198782}</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -8130,22 +8130,22 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>0.86514</v>
+        <v>0.8733599999999999</v>
       </c>
       <c r="F193" t="n">
-        <v>0.88088</v>
+        <v>0.88706</v>
       </c>
       <c r="G193" t="n">
-        <v>0.89116</v>
+        <v>0.8983800000000001</v>
       </c>
       <c r="H193" t="n">
-        <v>0.97434</v>
+        <v>0.9794599999999999</v>
       </c>
       <c r="I193" t="n">
-        <v>0.20118</v>
+        <v>0.1881</v>
       </c>
       <c r="J193" t="n">
-        <v>0.5413600000000001</v>
+        <v>0.5591799999999999</v>
       </c>
     </row>
     <row r="194">
@@ -8170,22 +8170,22 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>0.15854</v>
+        <v>0.15646</v>
       </c>
       <c r="F194" t="n">
-        <v>0.16028</v>
+        <v>0.15822</v>
       </c>
       <c r="G194" t="n">
-        <v>0.3917</v>
+        <v>0.38856</v>
       </c>
       <c r="H194" t="n">
-        <v>0.73558</v>
+        <v>0.73454</v>
       </c>
       <c r="I194" t="n">
-        <v>0.18438</v>
+        <v>0.16388</v>
       </c>
       <c r="J194" t="n">
-        <v>0.52906</v>
+        <v>0.5564199999999999</v>
       </c>
     </row>
     <row r="195">
@@ -8210,22 +8210,22 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>0.34292</v>
+        <v>0.32034</v>
       </c>
       <c r="F195" t="n">
-        <v>0.36922</v>
+        <v>0.34564</v>
       </c>
       <c r="G195" t="n">
-        <v>0.55178</v>
+        <v>0.5477000000000001</v>
       </c>
       <c r="H195" t="n">
         <v>0.8348599999999999</v>
       </c>
       <c r="I195" t="n">
-        <v>0.18438</v>
+        <v>0.16388</v>
       </c>
       <c r="J195" t="n">
-        <v>0.52906</v>
+        <v>0.5564199999999999</v>
       </c>
     </row>
     <row r="196">
@@ -8250,22 +8250,22 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>0.87198</v>
+        <v>0.87676</v>
       </c>
       <c r="F196" t="n">
-        <v>0.89374</v>
+        <v>0.8973000000000001</v>
       </c>
       <c r="G196" t="n">
-        <v>0.8860199999999999</v>
+        <v>0.8921999999999999</v>
       </c>
       <c r="H196" t="n">
-        <v>0.98458</v>
+        <v>0.9856</v>
       </c>
       <c r="I196" t="n">
-        <v>0.18438</v>
+        <v>0.16388</v>
       </c>
       <c r="J196" t="n">
-        <v>0.52906</v>
+        <v>0.5564199999999999</v>
       </c>
     </row>
     <row r="197">
@@ -8290,22 +8290,22 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>0.12874</v>
+        <v>0.12804</v>
       </c>
       <c r="F197" t="n">
-        <v>0.13012</v>
+        <v>0.12908</v>
       </c>
       <c r="G197" t="n">
-        <v>0.36458</v>
+        <v>0.36356</v>
       </c>
       <c r="H197" t="n">
-        <v>0.7127599999999999</v>
+        <v>0.71172</v>
       </c>
       <c r="I197" t="n">
-        <v>0.20184</v>
+        <v>0.1998400000000001</v>
       </c>
       <c r="J197" t="n">
-        <v>0.53184</v>
+        <v>0.53796</v>
       </c>
     </row>
     <row r="198">
@@ -8330,22 +8330,22 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>0.33058</v>
+        <v>0.3278800000000001</v>
       </c>
       <c r="F198" t="n">
-        <v>0.35078</v>
+        <v>0.3441</v>
       </c>
       <c r="G198" t="n">
-        <v>0.5425599999999999</v>
+        <v>0.55182</v>
       </c>
       <c r="H198" t="n">
-        <v>0.8102599999999999</v>
+        <v>0.8051199999999999</v>
       </c>
       <c r="I198" t="n">
-        <v>0.20184</v>
+        <v>0.1998400000000001</v>
       </c>
       <c r="J198" t="n">
-        <v>0.53184</v>
+        <v>0.53796</v>
       </c>
     </row>
     <row r="199">
@@ -8370,22 +8370,22 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>0.86242</v>
+        <v>0.8658400000000001</v>
       </c>
       <c r="F199" t="n">
-        <v>0.8783000000000001</v>
+        <v>0.8808999999999999</v>
       </c>
       <c r="G199" t="n">
         <v>0.89116</v>
       </c>
       <c r="H199" t="n">
-        <v>0.96716</v>
+        <v>0.9722799999999999</v>
       </c>
       <c r="I199" t="n">
-        <v>0.20184</v>
+        <v>0.1998400000000001</v>
       </c>
       <c r="J199" t="n">
-        <v>0.53184</v>
+        <v>0.53796</v>
       </c>
     </row>
     <row r="200">
@@ -8401,7 +8401,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}</t>
+          <t>{"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -8410,22 +8410,22 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>0.16868</v>
+        <v>0.1604</v>
       </c>
       <c r="F200" t="n">
-        <v>0.17556</v>
+        <v>0.16784</v>
       </c>
       <c r="G200" t="n">
-        <v>0.3708</v>
+        <v>0.36464</v>
       </c>
       <c r="H200" t="n">
-        <v>0.7230599999999999</v>
+        <v>0.71792</v>
       </c>
       <c r="I200" t="n">
-        <v>0.13662</v>
+        <v>0.1449</v>
       </c>
       <c r="J200" t="n">
-        <v>0.5440999999999999</v>
+        <v>0.553</v>
       </c>
     </row>
     <row r="201">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}</t>
+          <t>{"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -8453,19 +8453,19 @@
         <v>0.3053</v>
       </c>
       <c r="F201" t="n">
-        <v>0.32052</v>
+        <v>0.32204</v>
       </c>
       <c r="G201" t="n">
-        <v>0.5251399999999999</v>
+        <v>0.54154</v>
       </c>
       <c r="H201" t="n">
-        <v>0.8061800000000001</v>
+        <v>0.79794</v>
       </c>
       <c r="I201" t="n">
-        <v>0.13662</v>
+        <v>0.1449</v>
       </c>
       <c r="J201" t="n">
-        <v>0.5440999999999999</v>
+        <v>0.553</v>
       </c>
     </row>
     <row r="202">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}</t>
+          <t>{"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -8490,22 +8490,22 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>0.8493999999999999</v>
+        <v>0.8583000000000001</v>
       </c>
       <c r="F202" t="n">
-        <v>0.8696200000000001</v>
+        <v>0.8768</v>
       </c>
       <c r="G202" t="n">
-        <v>0.8747400000000001</v>
+        <v>0.87578</v>
       </c>
       <c r="H202" t="n">
-        <v>0.9692000000000001</v>
+        <v>0.9753599999999999</v>
       </c>
       <c r="I202" t="n">
-        <v>0.13662</v>
+        <v>0.1449</v>
       </c>
       <c r="J202" t="n">
-        <v>0.5440999999999999</v>
+        <v>0.553</v>
       </c>
     </row>
     <row r="203">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}}</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -8530,22 +8530,22 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>0.08891999999999999</v>
+        <v>0.09029999999999999</v>
       </c>
       <c r="F203" t="n">
-        <v>0.08838</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="G203" t="n">
-        <v>0.34404</v>
+        <v>0.34612</v>
       </c>
       <c r="H203" t="n">
-        <v>0.70766</v>
+        <v>0.70662</v>
       </c>
       <c r="I203" t="n">
-        <v>0.26356</v>
+        <v>0.2594400000000001</v>
       </c>
       <c r="J203" t="n">
-        <v>0.5414</v>
+        <v>0.5517</v>
       </c>
     </row>
     <row r="204">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}}</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -8570,22 +8570,22 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>0.35248</v>
+        <v>0.3497400000000001</v>
       </c>
       <c r="F204" t="n">
-        <v>0.3764</v>
+        <v>0.3718</v>
       </c>
       <c r="G204" t="n">
-        <v>0.5476800000000001</v>
+        <v>0.56206</v>
       </c>
       <c r="H204" t="n">
-        <v>0.8399999999999999</v>
+        <v>0.8328199999999999</v>
       </c>
       <c r="I204" t="n">
-        <v>0.26356</v>
+        <v>0.2594400000000001</v>
       </c>
       <c r="J204" t="n">
-        <v>0.5414</v>
+        <v>0.5517</v>
       </c>
     </row>
     <row r="205">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}}</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -8610,22 +8610,22 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>0.89388</v>
+        <v>0.90144</v>
       </c>
       <c r="F205" t="n">
-        <v>0.9091400000000001</v>
+        <v>0.91476</v>
       </c>
       <c r="G205" t="n">
-        <v>0.92506</v>
+        <v>0.9322199999999998</v>
       </c>
       <c r="H205" t="n">
-        <v>0.98254</v>
+        <v>0.98766</v>
       </c>
       <c r="I205" t="n">
-        <v>0.26356</v>
+        <v>0.2594400000000001</v>
       </c>
       <c r="J205" t="n">
-        <v>0.5414</v>
+        <v>0.5517</v>
       </c>
     </row>
     <row r="206">
@@ -8662,10 +8662,10 @@
         <v>0.77782</v>
       </c>
       <c r="I206" t="n">
-        <v>0.18738</v>
+        <v>0.16618</v>
       </c>
       <c r="J206" t="n">
-        <v>0.49292</v>
+        <v>0.51412</v>
       </c>
     </row>
     <row r="207">
@@ -8690,22 +8690,22 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>0.43316</v>
+        <v>0.41196</v>
       </c>
       <c r="F207" t="n">
-        <v>0.46616</v>
+        <v>0.44308</v>
       </c>
       <c r="G207" t="n">
-        <v>0.6</v>
+        <v>0.59076</v>
       </c>
       <c r="H207" t="n">
-        <v>0.8748800000000001</v>
+        <v>0.8707800000000001</v>
       </c>
       <c r="I207" t="n">
-        <v>0.18738</v>
+        <v>0.16618</v>
       </c>
       <c r="J207" t="n">
-        <v>0.49292</v>
+        <v>0.51412</v>
       </c>
     </row>
     <row r="208">
@@ -8733,19 +8733,19 @@
         <v>0.92608</v>
       </c>
       <c r="F208" t="n">
-        <v>0.9343</v>
+        <v>0.93428</v>
       </c>
       <c r="G208" t="n">
-        <v>0.9363400000000001</v>
+        <v>0.9363199999999999</v>
       </c>
       <c r="H208" t="n">
         <v>0.9815200000000001</v>
       </c>
       <c r="I208" t="n">
-        <v>0.18738</v>
+        <v>0.16618</v>
       </c>
       <c r="J208" t="n">
-        <v>0.49292</v>
+        <v>0.51412</v>
       </c>
     </row>
     <row r="209">
@@ -8782,10 +8782,10 @@
         <v>0.7820199999999999</v>
       </c>
       <c r="I209" t="n">
-        <v>0.09627999999999992</v>
+        <v>0.07507999999999998</v>
       </c>
       <c r="J209" t="n">
-        <v>0.551</v>
+        <v>0.5722</v>
       </c>
     </row>
     <row r="210">
@@ -8810,22 +8810,22 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>0.35386</v>
+        <v>0.33266</v>
       </c>
       <c r="F210" t="n">
-        <v>0.3728399999999999</v>
+        <v>0.3497400000000001</v>
       </c>
       <c r="G210" t="n">
-        <v>0.5353600000000001</v>
+        <v>0.5261400000000001</v>
       </c>
       <c r="H210" t="n">
-        <v>0.81334</v>
+        <v>0.80924</v>
       </c>
       <c r="I210" t="n">
-        <v>0.09627999999999992</v>
+        <v>0.07507999999999998</v>
       </c>
       <c r="J210" t="n">
-        <v>0.551</v>
+        <v>0.5722</v>
       </c>
     </row>
     <row r="211">
@@ -8853,7 +8853,7 @@
         <v>0.90486</v>
       </c>
       <c r="F211" t="n">
-        <v>0.9158199999999999</v>
+        <v>0.9158200000000001</v>
       </c>
       <c r="G211" t="n">
         <v>0.9117</v>
@@ -8862,10 +8862,10 @@
         <v>0.9774200000000001</v>
       </c>
       <c r="I211" t="n">
-        <v>0.09627999999999992</v>
+        <v>0.07507999999999998</v>
       </c>
       <c r="J211" t="n">
-        <v>0.551</v>
+        <v>0.5722</v>
       </c>
     </row>
     <row r="212">
@@ -8902,10 +8902,10 @@
         <v>0.6932</v>
       </c>
       <c r="I212" t="n">
-        <v>0.16508</v>
+        <v>0.14664</v>
       </c>
       <c r="J212" t="n">
-        <v>0.6398799999999999</v>
+        <v>0.65218</v>
       </c>
     </row>
     <row r="213">
@@ -8930,22 +8930,22 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>0.2588</v>
+        <v>0.24036</v>
       </c>
       <c r="F213" t="n">
-        <v>0.28564</v>
+        <v>0.26206</v>
       </c>
       <c r="G213" t="n">
-        <v>0.4871800000000001</v>
+        <v>0.49026</v>
       </c>
       <c r="H213" t="n">
-        <v>0.80616</v>
+        <v>0.78976</v>
       </c>
       <c r="I213" t="n">
-        <v>0.16508</v>
+        <v>0.14664</v>
       </c>
       <c r="J213" t="n">
-        <v>0.6398799999999999</v>
+        <v>0.65218</v>
       </c>
     </row>
     <row r="214">
@@ -8970,22 +8970,22 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>0.8986799999999999</v>
+        <v>0.89254</v>
       </c>
       <c r="F214" t="n">
-        <v>0.9157999999999999</v>
+        <v>0.9111799999999999</v>
       </c>
       <c r="G214" t="n">
-        <v>0.91578</v>
+        <v>0.9096399999999999</v>
       </c>
       <c r="H214" t="n">
         <v>0.9887</v>
       </c>
       <c r="I214" t="n">
-        <v>0.16508</v>
+        <v>0.14664</v>
       </c>
       <c r="J214" t="n">
-        <v>0.6398799999999999</v>
+        <v>0.65218</v>
       </c>
     </row>
     <row r="215">
@@ -9010,22 +9010,22 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>0.08892</v>
+        <v>0.08821999999999999</v>
       </c>
       <c r="F215" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.08734</v>
       </c>
       <c r="G215" t="n">
-        <v>0.343</v>
+        <v>0.342</v>
       </c>
       <c r="H215" t="n">
-        <v>0.7087</v>
+        <v>0.70766</v>
       </c>
       <c r="I215" t="n">
-        <v>0.26562</v>
+        <v>0.25878</v>
       </c>
       <c r="J215" t="n">
-        <v>0.538</v>
+        <v>0.5489400000000001</v>
       </c>
     </row>
     <row r="216">
@@ -9050,22 +9050,22 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>0.35454</v>
+        <v>0.347</v>
       </c>
       <c r="F216" t="n">
-        <v>0.37898</v>
+        <v>0.36874</v>
       </c>
       <c r="G216" t="n">
-        <v>0.54972</v>
+        <v>0.5599999999999999</v>
       </c>
       <c r="H216" t="n">
-        <v>0.8410399999999999</v>
+        <v>0.8297399999999999</v>
       </c>
       <c r="I216" t="n">
-        <v>0.26562</v>
+        <v>0.25878</v>
       </c>
       <c r="J216" t="n">
-        <v>0.538</v>
+        <v>0.5489400000000001</v>
       </c>
     </row>
     <row r="217">
@@ -9090,22 +9090,22 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>0.89254</v>
+        <v>0.8959400000000001</v>
       </c>
       <c r="F217" t="n">
-        <v>0.9080999999999999</v>
+        <v>0.9106799999999999</v>
       </c>
       <c r="G217" t="n">
         <v>0.924</v>
       </c>
       <c r="H217" t="n">
-        <v>0.98254</v>
+        <v>0.98766</v>
       </c>
       <c r="I217" t="n">
-        <v>0.26562</v>
+        <v>0.25878</v>
       </c>
       <c r="J217" t="n">
-        <v>0.538</v>
+        <v>0.5489400000000001</v>
       </c>
     </row>
     <row r="218">
@@ -9142,10 +9142,10 @@
         <v>0.6974400000000001</v>
       </c>
       <c r="I218" t="n">
-        <v>0.12862</v>
+        <v>0.1338</v>
       </c>
       <c r="J218" t="n">
-        <v>0.61876</v>
+        <v>0.6135799999999999</v>
       </c>
     </row>
     <row r="219">
@@ -9170,22 +9170,22 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>0.30468</v>
+        <v>0.30986</v>
       </c>
       <c r="F219" t="n">
-        <v>0.32038</v>
+        <v>0.328</v>
       </c>
       <c r="G219" t="n">
-        <v>0.4722000000000001</v>
+        <v>0.48708</v>
       </c>
       <c r="H219" t="n">
-        <v>0.79366</v>
+        <v>0.79582</v>
       </c>
       <c r="I219" t="n">
-        <v>0.12862</v>
+        <v>0.1338</v>
       </c>
       <c r="J219" t="n">
-        <v>0.61876</v>
+        <v>0.6135799999999999</v>
       </c>
     </row>
     <row r="220">
@@ -9222,10 +9222,10 @@
         <v>0.9846</v>
       </c>
       <c r="I220" t="n">
-        <v>0.12862</v>
+        <v>0.1338</v>
       </c>
       <c r="J220" t="n">
-        <v>0.61876</v>
+        <v>0.6135799999999999</v>
       </c>
     </row>
     <row r="221">
@@ -9250,22 +9250,22 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>0.19316</v>
+        <v>0.1966</v>
       </c>
       <c r="F221" t="n">
-        <v>0.20102</v>
+        <v>0.2036</v>
       </c>
       <c r="G221" t="n">
-        <v>0.3804999999999999</v>
+        <v>0.38562</v>
       </c>
       <c r="H221" t="n">
         <v>0.7220600000000001</v>
       </c>
       <c r="I221" t="n">
-        <v>0.10382</v>
+        <v>0.10362</v>
       </c>
       <c r="J221" t="n">
-        <v>0.5983999999999999</v>
+        <v>0.5986</v>
       </c>
     </row>
     <row r="222">
@@ -9290,22 +9290,22 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>0.29698</v>
+        <v>0.30022</v>
       </c>
       <c r="F222" t="n">
-        <v>0.32402</v>
+        <v>0.3233400000000001</v>
       </c>
       <c r="G222" t="n">
-        <v>0.44806</v>
+        <v>0.45184</v>
       </c>
       <c r="H222" t="n">
-        <v>0.7937</v>
+        <v>0.79586</v>
       </c>
       <c r="I222" t="n">
-        <v>0.10382</v>
+        <v>0.10362</v>
       </c>
       <c r="J222" t="n">
-        <v>0.5983999999999999</v>
+        <v>0.5986</v>
       </c>
     </row>
     <row r="223">
@@ -9330,22 +9330,22 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>0.89538</v>
+        <v>0.8988200000000001</v>
       </c>
       <c r="F223" t="n">
-        <v>0.90564</v>
+        <v>0.90822</v>
       </c>
       <c r="G223" t="n">
-        <v>0.91076</v>
+        <v>0.9158799999999999</v>
       </c>
       <c r="H223" t="n">
         <v>0.97334</v>
       </c>
       <c r="I223" t="n">
-        <v>0.10382</v>
+        <v>0.10362</v>
       </c>
       <c r="J223" t="n">
-        <v>0.5983999999999999</v>
+        <v>0.5986</v>
       </c>
     </row>
     <row r="224">
@@ -9370,10 +9370,10 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>0.20342</v>
+        <v>0.20274</v>
       </c>
       <c r="F224" t="n">
-        <v>0.19998</v>
+        <v>0.1995</v>
       </c>
       <c r="G224" t="n">
         <v>0.4041</v>
@@ -9382,10 +9382,10 @@
         <v>0.7076800000000001</v>
       </c>
       <c r="I224" t="n">
-        <v>0.1257</v>
+        <v>0.12786</v>
       </c>
       <c r="J224" t="n">
-        <v>0.6086799999999999</v>
+        <v>0.6106199999999998</v>
       </c>
     </row>
     <row r="225">
@@ -9410,22 +9410,22 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>0.32912</v>
+        <v>0.3306</v>
       </c>
       <c r="F225" t="n">
-        <v>0.35122</v>
+        <v>0.3534</v>
       </c>
       <c r="G225" t="n">
-        <v>0.50462</v>
+        <v>0.5057199999999999</v>
       </c>
       <c r="H225" t="n">
-        <v>0.7988799999999999</v>
+        <v>0.8010399999999999</v>
       </c>
       <c r="I225" t="n">
-        <v>0.1257</v>
+        <v>0.12786</v>
       </c>
       <c r="J225" t="n">
-        <v>0.6086799999999999</v>
+        <v>0.6106199999999998</v>
       </c>
     </row>
     <row r="226">
@@ -9450,22 +9450,22 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>0.9378</v>
+        <v>0.9412199999999998</v>
       </c>
       <c r="F226" t="n">
-        <v>0.95078</v>
+        <v>0.9533000000000001</v>
       </c>
       <c r="G226" t="n">
-        <v>0.9476800000000001</v>
+        <v>0.9527800000000001</v>
       </c>
       <c r="H226" t="n">
         <v>1</v>
       </c>
       <c r="I226" t="n">
-        <v>0.1257</v>
+        <v>0.12786</v>
       </c>
       <c r="J226" t="n">
-        <v>0.6086799999999999</v>
+        <v>0.6106199999999998</v>
       </c>
     </row>
     <row r="227">
@@ -9493,19 +9493,19 @@
         <v>0.1747</v>
       </c>
       <c r="F227" t="n">
-        <v>0.17642</v>
+        <v>0.17488</v>
       </c>
       <c r="G227" t="n">
-        <v>0.3558800000000001</v>
+        <v>0.36102</v>
       </c>
       <c r="H227" t="n">
         <v>0.6974199999999999</v>
       </c>
       <c r="I227" t="n">
-        <v>0.13698</v>
+        <v>0.1358799999999999</v>
       </c>
       <c r="J227" t="n">
-        <v>0.6007999999999998</v>
+        <v>0.6018999999999999</v>
       </c>
     </row>
     <row r="228">
@@ -9530,22 +9530,22 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>0.31168</v>
+        <v>0.31058</v>
       </c>
       <c r="F228" t="n">
-        <v>0.33034</v>
+        <v>0.32856</v>
       </c>
       <c r="G228" t="n">
-        <v>0.47008</v>
+        <v>0.47878</v>
       </c>
       <c r="H228" t="n">
-        <v>0.7811399999999999</v>
+        <v>0.7834399999999999</v>
       </c>
       <c r="I228" t="n">
-        <v>0.13698</v>
+        <v>0.1358799999999999</v>
       </c>
       <c r="J228" t="n">
-        <v>0.6007999999999998</v>
+        <v>0.6018999999999999</v>
       </c>
     </row>
     <row r="229">
@@ -9576,16 +9576,16 @@
         <v>0.92562</v>
       </c>
       <c r="G229" t="n">
-        <v>0.9169</v>
+        <v>0.92204</v>
       </c>
       <c r="H229" t="n">
         <v>0.98256</v>
       </c>
       <c r="I229" t="n">
-        <v>0.13698</v>
+        <v>0.1358799999999999</v>
       </c>
       <c r="J229" t="n">
-        <v>0.6007999999999998</v>
+        <v>0.6018999999999999</v>
       </c>
     </row>
     <row r="230">
@@ -9622,10 +9622,10 @@
         <v>0.71692</v>
       </c>
       <c r="I230" t="n">
-        <v>0.11192</v>
+        <v>0.11758</v>
       </c>
       <c r="J230" t="n">
-        <v>0.6142000000000001</v>
+        <v>0.6120399999999999</v>
       </c>
     </row>
     <row r="231">
@@ -9650,22 +9650,22 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>0.3208</v>
+        <v>0.32646</v>
       </c>
       <c r="F231" t="n">
-        <v>0.34292</v>
+        <v>0.34928</v>
       </c>
       <c r="G231" t="n">
-        <v>0.4962799999999999</v>
+        <v>0.49744</v>
       </c>
       <c r="H231" t="n">
-        <v>0.7999599999999999</v>
+        <v>0.8020799999999999</v>
       </c>
       <c r="I231" t="n">
-        <v>0.11192</v>
+        <v>0.11758</v>
       </c>
       <c r="J231" t="n">
-        <v>0.6142000000000001</v>
+        <v>0.6120399999999999</v>
       </c>
     </row>
     <row r="232">
@@ -9690,22 +9690,22 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>0.9350000000000002</v>
+        <v>0.9385</v>
       </c>
       <c r="F232" t="n">
+        <v>0.9513</v>
+      </c>
+      <c r="G232" t="n">
         <v>0.9487</v>
-      </c>
-      <c r="G232" t="n">
-        <v>0.9436</v>
       </c>
       <c r="H232" t="n">
         <v>1</v>
       </c>
       <c r="I232" t="n">
-        <v>0.11192</v>
+        <v>0.11758</v>
       </c>
       <c r="J232" t="n">
-        <v>0.6142000000000001</v>
+        <v>0.6120399999999999</v>
       </c>
     </row>
     <row r="233">
@@ -9730,22 +9730,22 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>0.19864</v>
+        <v>0.19932</v>
       </c>
       <c r="F233" t="n">
-        <v>0.1954</v>
+        <v>0.19744</v>
       </c>
       <c r="G233" t="n">
-        <v>0.4051</v>
+        <v>0.40306</v>
       </c>
       <c r="H233" t="n">
-        <v>0.7128</v>
+        <v>0.7179399999999999</v>
       </c>
       <c r="I233" t="n">
-        <v>0.12842</v>
+        <v>0.1375</v>
       </c>
       <c r="J233" t="n">
-        <v>0.6025</v>
+        <v>0.59274</v>
       </c>
     </row>
     <row r="234">
@@ -9770,22 +9770,22 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>0.32706</v>
+        <v>0.33682</v>
       </c>
       <c r="F234" t="n">
-        <v>0.34448</v>
+        <v>0.35082</v>
       </c>
       <c r="G234" t="n">
-        <v>0.49212</v>
+        <v>0.50262</v>
       </c>
       <c r="H234" t="n">
-        <v>0.8010400000000001</v>
+        <v>0.8</v>
       </c>
       <c r="I234" t="n">
-        <v>0.12842</v>
+        <v>0.1375</v>
       </c>
       <c r="J234" t="n">
-        <v>0.6025</v>
+        <v>0.59274</v>
       </c>
     </row>
     <row r="235">
@@ -9813,19 +9813,19 @@
         <v>0.9295600000000001</v>
       </c>
       <c r="F235" t="n">
-        <v>0.9420399999999999</v>
+        <v>0.9395</v>
       </c>
       <c r="G235" t="n">
         <v>0.94564</v>
       </c>
       <c r="H235" t="n">
-        <v>0.9949</v>
+        <v>0.9897</v>
       </c>
       <c r="I235" t="n">
-        <v>0.12842</v>
+        <v>0.1375</v>
       </c>
       <c r="J235" t="n">
-        <v>0.6025</v>
+        <v>0.59274</v>
       </c>
     </row>
     <row r="236">
@@ -9850,22 +9850,22 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>0.20408</v>
+        <v>0.20754</v>
       </c>
       <c r="F236" t="n">
-        <v>0.2164</v>
+        <v>0.21898</v>
       </c>
       <c r="G236" t="n">
-        <v>0.37848</v>
+        <v>0.38358</v>
       </c>
       <c r="H236" t="n">
         <v>0.72</v>
       </c>
       <c r="I236" t="n">
-        <v>0.1181</v>
+        <v>0.121</v>
       </c>
       <c r="J236" t="n">
-        <v>0.5697799999999998</v>
+        <v>0.5668600000000001</v>
       </c>
     </row>
     <row r="237">
@@ -9890,22 +9890,22 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>0.32218</v>
+        <v>0.32854</v>
       </c>
       <c r="F237" t="n">
-        <v>0.3529</v>
+        <v>0.35444</v>
       </c>
       <c r="G237" t="n">
-        <v>0.45546</v>
+        <v>0.4643</v>
       </c>
       <c r="H237" t="n">
-        <v>0.7989599999999999</v>
+        <v>0.8010200000000001</v>
       </c>
       <c r="I237" t="n">
-        <v>0.1181</v>
+        <v>0.121</v>
       </c>
       <c r="J237" t="n">
-        <v>0.5697799999999998</v>
+        <v>0.5668600000000001</v>
       </c>
     </row>
     <row r="238">
@@ -9930,22 +9930,22 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>0.8919599999999999</v>
+        <v>0.8954000000000001</v>
       </c>
       <c r="F238" t="n">
-        <v>0.90464</v>
+        <v>0.90718</v>
       </c>
       <c r="G238" t="n">
-        <v>0.9056599999999999</v>
+        <v>0.91076</v>
       </c>
       <c r="H238" t="n">
         <v>0.97644</v>
       </c>
       <c r="I238" t="n">
-        <v>0.1181</v>
+        <v>0.121</v>
       </c>
       <c r="J238" t="n">
-        <v>0.5697799999999998</v>
+        <v>0.5668600000000001</v>
       </c>
     </row>
     <row r="239">
@@ -9970,10 +9970,10 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>0.2048</v>
+        <v>0.20546</v>
       </c>
       <c r="F239" t="n">
-        <v>0.20154</v>
+        <v>0.20204</v>
       </c>
       <c r="G239" t="n">
         <v>0.39486</v>
@@ -9982,10 +9982,10 @@
         <v>0.7107599999999999</v>
       </c>
       <c r="I239" t="n">
-        <v>0.11596</v>
+        <v>0.12514</v>
       </c>
       <c r="J239" t="n">
-        <v>0.6163399999999999</v>
+        <v>0.6099400000000001</v>
       </c>
     </row>
     <row r="240">
@@ -10010,22 +10010,22 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>0.32076</v>
+        <v>0.3305999999999999</v>
       </c>
       <c r="F240" t="n">
-        <v>0.33816</v>
+        <v>0.3467</v>
       </c>
       <c r="G240" t="n">
-        <v>0.48578</v>
+        <v>0.4871</v>
       </c>
       <c r="H240" t="n">
-        <v>0.7947200000000001</v>
+        <v>0.79686</v>
       </c>
       <c r="I240" t="n">
-        <v>0.11596</v>
+        <v>0.12514</v>
       </c>
       <c r="J240" t="n">
-        <v>0.6163399999999999</v>
+        <v>0.6099400000000001</v>
       </c>
     </row>
     <row r="241">
@@ -10050,10 +10050,10 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>0.9370999999999998</v>
+        <v>0.94054</v>
       </c>
       <c r="F241" t="n">
-        <v>0.9502599999999999</v>
+        <v>0.95536</v>
       </c>
       <c r="G241" t="n">
         <v>0.9466599999999999</v>
@@ -10062,10 +10062,10 @@
         <v>1</v>
       </c>
       <c r="I241" t="n">
-        <v>0.11596</v>
+        <v>0.12514</v>
       </c>
       <c r="J241" t="n">
-        <v>0.6163399999999999</v>
+        <v>0.6099400000000001</v>
       </c>
     </row>
     <row r="242">
@@ -10090,10 +10090,10 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>0.1658</v>
+        <v>0.16236</v>
       </c>
       <c r="F242" t="n">
-        <v>0.17128</v>
+        <v>0.16718</v>
       </c>
       <c r="G242" t="n">
         <v>0.35488</v>
@@ -10102,10 +10102,10 @@
         <v>0.7118</v>
       </c>
       <c r="I242" t="n">
-        <v>0.14372</v>
+        <v>0.13784</v>
       </c>
       <c r="J242" t="n">
-        <v>0.6049800000000001</v>
+        <v>0.6109</v>
       </c>
     </row>
     <row r="243">
@@ -10130,22 +10130,22 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>0.30952</v>
+        <v>0.3002</v>
       </c>
       <c r="F243" t="n">
-        <v>0.3282</v>
+        <v>0.3202199999999999</v>
       </c>
       <c r="G243" t="n">
-        <v>0.4721</v>
+        <v>0.4705</v>
       </c>
       <c r="H243" t="n">
-        <v>0.78116</v>
+        <v>0.7782600000000001</v>
       </c>
       <c r="I243" t="n">
-        <v>0.14372</v>
+        <v>0.13784</v>
       </c>
       <c r="J243" t="n">
-        <v>0.6049800000000001</v>
+        <v>0.6109</v>
       </c>
     </row>
     <row r="244">
@@ -10170,10 +10170,10 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>0.9145</v>
+        <v>0.9111</v>
       </c>
       <c r="F244" t="n">
-        <v>0.9256</v>
+        <v>0.9231</v>
       </c>
       <c r="G244" t="n">
         <v>0.9333</v>
@@ -10182,10 +10182,10 @@
         <v>0.9795</v>
       </c>
       <c r="I244" t="n">
-        <v>0.14372</v>
+        <v>0.13784</v>
       </c>
       <c r="J244" t="n">
-        <v>0.6049800000000001</v>
+        <v>0.6109</v>
       </c>
     </row>
     <row r="245">
@@ -10210,10 +10210,10 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>0.3087</v>
+        <v>0.31216</v>
       </c>
       <c r="F245" t="n">
-        <v>0.32668</v>
+        <v>0.32974</v>
       </c>
       <c r="G245" t="n">
         <v>0.4995</v>
@@ -10222,10 +10222,10 @@
         <v>0.79794</v>
       </c>
       <c r="I245" t="n">
-        <v>0.07979999999999998</v>
+        <v>0.07714000000000004</v>
       </c>
       <c r="J245" t="n">
-        <v>0.5363</v>
+        <v>0.5218</v>
       </c>
     </row>
     <row r="246">
@@ -10250,22 +10250,22 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>0.3885</v>
+        <v>0.3893</v>
       </c>
       <c r="F246" t="n">
-        <v>0.42148</v>
+        <v>0.42278</v>
       </c>
       <c r="G246" t="n">
-        <v>0.55284</v>
+        <v>0.5502800000000001</v>
       </c>
       <c r="H246" t="n">
-        <v>0.8460800000000001</v>
+        <v>0.8455999999999999</v>
       </c>
       <c r="I246" t="n">
-        <v>0.07979999999999998</v>
+        <v>0.07714000000000004</v>
       </c>
       <c r="J246" t="n">
-        <v>0.5363</v>
+        <v>0.5218</v>
       </c>
     </row>
     <row r="247">
@@ -10290,22 +10290,22 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>0.9248</v>
+        <v>0.9111</v>
       </c>
       <c r="F247" t="n">
+        <v>0.9333199999999999</v>
+      </c>
+      <c r="G247" t="n">
         <v>0.9436</v>
-      </c>
-      <c r="G247" t="n">
-        <v>0.9487</v>
       </c>
       <c r="H247" t="n">
         <v>1</v>
       </c>
       <c r="I247" t="n">
-        <v>0.07979999999999998</v>
+        <v>0.07714000000000004</v>
       </c>
       <c r="J247" t="n">
-        <v>0.5363</v>
+        <v>0.5218</v>
       </c>
     </row>
     <row r="248">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.194172, "environmental": 0.131673, "comfort": 0.401912, "practicality": 0.272243}</t>
+          <t>{"energy_cost": 0.1943, "environmental": 0.131354, "comfort": 0.403745, "practicality": 0.2706}</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -10330,22 +10330,22 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>0.6547000000000001</v>
+        <v>0.6553800000000001</v>
       </c>
       <c r="F248" t="n">
-        <v>0.7045999999999999</v>
+        <v>0.70512</v>
       </c>
       <c r="G248" t="n">
-        <v>0.7559</v>
+        <v>0.75692</v>
       </c>
       <c r="H248" t="n">
         <v>0.95076</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.03864000000000012</v>
+        <v>-0.02356000000000003</v>
       </c>
       <c r="J248" t="n">
-        <v>0.3155399999999999</v>
+        <v>0.3237599999999999</v>
       </c>
     </row>
     <row r="249">
@@ -10361,7 +10361,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.194172, "environmental": 0.131673, "comfort": 0.401912, "practicality": 0.272243}</t>
+          <t>{"energy_cost": 0.1943, "environmental": 0.131354, "comfort": 0.403745, "practicality": 0.2706}</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -10370,22 +10370,22 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>0.6160599999999999</v>
+        <v>0.63182</v>
       </c>
       <c r="F249" t="n">
-        <v>0.65654</v>
+        <v>0.6787600000000001</v>
       </c>
       <c r="G249" t="n">
-        <v>0.7423999999999999</v>
+        <v>0.7440599999999999</v>
       </c>
       <c r="H249" t="n">
-        <v>0.91522</v>
+        <v>0.9336800000000001</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.03864000000000012</v>
+        <v>-0.02356000000000003</v>
       </c>
       <c r="J249" t="n">
-        <v>0.3155399999999999</v>
+        <v>0.3237599999999999</v>
       </c>
     </row>
     <row r="250">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.194172, "environmental": 0.131673, "comfort": 0.401912, "practicality": 0.272243}</t>
+          <t>{"energy_cost": 0.1943, "environmental": 0.131354, "comfort": 0.403745, "practicality": 0.2706}</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -10410,22 +10410,22 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>0.9315999999999999</v>
+        <v>0.95558</v>
       </c>
       <c r="F250" t="n">
-        <v>0.94872</v>
+        <v>0.96668</v>
       </c>
       <c r="G250" t="n">
-        <v>0.9220599999999999</v>
+        <v>0.9527800000000001</v>
       </c>
       <c r="H250" t="n">
         <v>1</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.03864000000000012</v>
+        <v>-0.02356000000000003</v>
       </c>
       <c r="J250" t="n">
-        <v>0.3155399999999999</v>
+        <v>0.3237599999999999</v>
       </c>
     </row>
     <row r="251">
@@ -10462,10 +10462,10 @@
         <v>0.9610200000000001</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.07232000000000005</v>
+        <v>-0.07588000000000006</v>
       </c>
       <c r="J251" t="n">
-        <v>0.3676600000000001</v>
+        <v>0.3849199999999999</v>
       </c>
     </row>
     <row r="252">
@@ -10490,22 +10490,22 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>0.60358</v>
+        <v>0.60002</v>
       </c>
       <c r="F252" t="n">
-        <v>0.64878</v>
+        <v>0.6461</v>
       </c>
       <c r="G252" t="n">
-        <v>0.7329799999999999</v>
+        <v>0.715</v>
       </c>
       <c r="H252" t="n">
-        <v>0.92878</v>
+        <v>0.93574</v>
       </c>
       <c r="I252" t="n">
-        <v>-0.07232000000000005</v>
+        <v>-0.07588000000000006</v>
       </c>
       <c r="J252" t="n">
-        <v>0.3676600000000001</v>
+        <v>0.3849199999999999</v>
       </c>
     </row>
     <row r="253">
@@ -10530,22 +10530,22 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>0.9712400000000001</v>
+        <v>0.9849399999999999</v>
       </c>
       <c r="F253" t="n">
-        <v>0.9784599999999999</v>
+        <v>0.9887</v>
       </c>
       <c r="G253" t="n">
-        <v>0.9641</v>
+        <v>0.9846</v>
       </c>
       <c r="H253" t="n">
         <v>1</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.07232000000000005</v>
+        <v>-0.07588000000000006</v>
       </c>
       <c r="J253" t="n">
-        <v>0.3676600000000001</v>
+        <v>0.3849199999999999</v>
       </c>
     </row>
     <row r="254">
@@ -10582,10 +10582,10 @@
         <v>0.92204</v>
       </c>
       <c r="I254" t="n">
-        <v>0.01804000000000006</v>
+        <v>0.03895999999999999</v>
       </c>
       <c r="J254" t="n">
-        <v>0.3573200000000001</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="255">
@@ -10610,22 +10610,22 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>0.5784</v>
+        <v>0.59932</v>
       </c>
       <c r="F255" t="n">
-        <v>0.6178399999999999</v>
+        <v>0.64198</v>
       </c>
       <c r="G255" t="n">
-        <v>0.72144</v>
+        <v>0.72644</v>
       </c>
       <c r="H255" t="n">
-        <v>0.8963199999999999</v>
+        <v>0.91604</v>
       </c>
       <c r="I255" t="n">
-        <v>0.01804000000000006</v>
+        <v>0.03895999999999999</v>
       </c>
       <c r="J255" t="n">
-        <v>0.3573200000000001</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="256">
@@ -10650,22 +10650,22 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>0.9357200000000001</v>
+        <v>0.95282</v>
       </c>
       <c r="F256" t="n">
-        <v>0.95178</v>
+        <v>0.96462</v>
       </c>
       <c r="G256" t="n">
-        <v>0.9322800000000001</v>
+        <v>0.93746</v>
       </c>
       <c r="H256" t="n">
         <v>1</v>
       </c>
       <c r="I256" t="n">
-        <v>0.01804000000000006</v>
+        <v>0.03895999999999999</v>
       </c>
       <c r="J256" t="n">
-        <v>0.3573200000000001</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="257">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}</t>
+          <t>{"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -10690,22 +10690,22 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>0.3272</v>
+        <v>0.32992</v>
       </c>
       <c r="F257" t="n">
-        <v>0.34722</v>
+        <v>0.35128</v>
       </c>
       <c r="G257" t="n">
-        <v>0.4841</v>
+        <v>0.4882000000000001</v>
       </c>
       <c r="H257" t="n">
-        <v>0.8041</v>
+        <v>0.8092200000000001</v>
       </c>
       <c r="I257" t="n">
-        <v>0.03613999999999995</v>
+        <v>0.04002000000000006</v>
       </c>
       <c r="J257" t="n">
-        <v>0.55116</v>
+        <v>0.5343599999999998</v>
       </c>
     </row>
     <row r="258">
@@ -10721,7 +10721,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}</t>
+          <t>{"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -10730,22 +10730,22 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>0.36334</v>
+        <v>0.36994</v>
       </c>
       <c r="F258" t="n">
-        <v>0.3994200000000001</v>
+        <v>0.4103200000000001</v>
       </c>
       <c r="G258" t="n">
-        <v>0.53926</v>
+        <v>0.54922</v>
       </c>
       <c r="H258" t="n">
-        <v>0.8261200000000001</v>
+        <v>0.83212</v>
       </c>
       <c r="I258" t="n">
-        <v>0.03613999999999995</v>
+        <v>0.04002000000000006</v>
       </c>
       <c r="J258" t="n">
-        <v>0.55116</v>
+        <v>0.5343599999999998</v>
       </c>
     </row>
     <row r="259">
@@ -10761,7 +10761,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}</t>
+          <t>{"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -10770,22 +10770,22 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>0.9145</v>
+        <v>0.9042999999999999</v>
       </c>
       <c r="F259" t="n">
-        <v>0.9359</v>
+        <v>0.9282</v>
       </c>
       <c r="G259" t="n">
-        <v>0.9333400000000001</v>
+        <v>0.9230600000000001</v>
       </c>
       <c r="H259" t="n">
         <v>1</v>
       </c>
       <c r="I259" t="n">
-        <v>0.03613999999999995</v>
+        <v>0.04002000000000006</v>
       </c>
       <c r="J259" t="n">
-        <v>0.55116</v>
+        <v>0.5343599999999998</v>
       </c>
     </row>
     <row r="260">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}}</t>
+          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}}</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -10822,10 +10822,10 @@
         <v>0.94256</v>
       </c>
       <c r="I260" t="n">
-        <v>0.03156000000000014</v>
+        <v>0.02283999999999997</v>
       </c>
       <c r="J260" t="n">
-        <v>0.3055599999999999</v>
+        <v>0.3040000000000002</v>
       </c>
     </row>
     <row r="261">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}}</t>
+          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}}</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -10850,22 +10850,22 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.6248799999999999</v>
       </c>
       <c r="F261" t="n">
-        <v>0.6812199999999999</v>
+        <v>0.67462</v>
       </c>
       <c r="G261" t="n">
-        <v>0.7655399999999999</v>
+        <v>0.7605999999999999</v>
       </c>
       <c r="H261" t="n">
-        <v>0.9412800000000001</v>
+        <v>0.93782</v>
       </c>
       <c r="I261" t="n">
-        <v>0.03156000000000014</v>
+        <v>0.02283999999999997</v>
       </c>
       <c r="J261" t="n">
-        <v>0.3055599999999999</v>
+        <v>0.3040000000000002</v>
       </c>
     </row>
     <row r="262">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}}</t>
+          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}}</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -10890,22 +10890,22 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>0.93916</v>
+        <v>0.92888</v>
       </c>
       <c r="F262" t="n">
-        <v>0.95434</v>
+        <v>0.9466800000000001</v>
       </c>
       <c r="G262" t="n">
-        <v>0.9436</v>
+        <v>0.9385</v>
       </c>
       <c r="H262" t="n">
         <v>1</v>
       </c>
       <c r="I262" t="n">
-        <v>0.03156000000000014</v>
+        <v>0.02283999999999997</v>
       </c>
       <c r="J262" t="n">
-        <v>0.3055599999999999</v>
+        <v>0.3040000000000002</v>
       </c>
     </row>
     <row r="263">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.268909, "environmental": 0.371359, "comfort": 0.160782, "practicality": 0.19895}</t>
+          <t>{"energy_cost": 0.268683, "environmental": 0.371046, "comfort": 0.16149, "practicality": 0.198782}</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -10933,19 +10933,19 @@
         <v>0.19726</v>
       </c>
       <c r="F263" t="n">
-        <v>0.18976</v>
+        <v>0.19128</v>
       </c>
       <c r="G263" t="n">
-        <v>0.37642</v>
+        <v>0.37538</v>
       </c>
       <c r="H263" t="n">
-        <v>0.7015399999999999</v>
+        <v>0.70462</v>
       </c>
       <c r="I263" t="n">
-        <v>0.13326</v>
+        <v>0.13334</v>
       </c>
       <c r="J263" t="n">
-        <v>0.57786</v>
+        <v>0.5880200000000001</v>
       </c>
     </row>
     <row r="264">
@@ -10961,7 +10961,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.268909, "environmental": 0.371359, "comfort": 0.160782, "practicality": 0.19895}</t>
+          <t>{"energy_cost": 0.268683, "environmental": 0.371046, "comfort": 0.16149, "practicality": 0.198782}</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -10970,22 +10970,22 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>0.33052</v>
+        <v>0.3306</v>
       </c>
       <c r="F264" t="n">
-        <v>0.34496</v>
+        <v>0.34822</v>
       </c>
       <c r="G264" t="n">
-        <v>0.48792</v>
+        <v>0.4891599999999999</v>
       </c>
       <c r="H264" t="n">
-        <v>0.7988999999999999</v>
+        <v>0.80102</v>
       </c>
       <c r="I264" t="n">
-        <v>0.13326</v>
+        <v>0.13334</v>
       </c>
       <c r="J264" t="n">
-        <v>0.57786</v>
+        <v>0.5880200000000001</v>
       </c>
     </row>
     <row r="265">
@@ -11001,7 +11001,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.268909, "environmental": 0.371359, "comfort": 0.160782, "practicality": 0.19895}</t>
+          <t>{"energy_cost": 0.268683, "environmental": 0.371046, "comfort": 0.16149, "practicality": 0.198782}</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -11010,22 +11010,22 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>0.90838</v>
+        <v>0.9186200000000001</v>
       </c>
       <c r="F265" t="n">
-        <v>0.9220200000000001</v>
+        <v>0.92972</v>
       </c>
       <c r="G265" t="n">
-        <v>0.9271800000000001</v>
+        <v>0.9374600000000001</v>
       </c>
       <c r="H265" t="n">
-        <v>0.9866400000000001</v>
+        <v>0.99178</v>
       </c>
       <c r="I265" t="n">
-        <v>0.13326</v>
+        <v>0.13334</v>
       </c>
       <c r="J265" t="n">
-        <v>0.57786</v>
+        <v>0.5880200000000001</v>
       </c>
     </row>
     <row r="266">
@@ -11050,22 +11050,22 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>0.15966</v>
+        <v>0.16308</v>
       </c>
       <c r="F266" t="n">
-        <v>0.16516</v>
+        <v>0.16768</v>
       </c>
       <c r="G266" t="n">
-        <v>0.36514</v>
+        <v>0.37026</v>
       </c>
       <c r="H266" t="n">
         <v>0.7036</v>
       </c>
       <c r="I266" t="n">
-        <v>0.14784</v>
+        <v>0.15094</v>
       </c>
       <c r="J266" t="n">
-        <v>0.5878599999999999</v>
+        <v>0.5847800000000002</v>
       </c>
     </row>
     <row r="267">
@@ -11090,22 +11090,22 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>0.3075</v>
+        <v>0.31402</v>
       </c>
       <c r="F267" t="n">
-        <v>0.32562</v>
+        <v>0.33216</v>
       </c>
       <c r="G267" t="n">
-        <v>0.4764200000000001</v>
+        <v>0.48294</v>
       </c>
       <c r="H267" t="n">
-        <v>0.7884599999999999</v>
+        <v>0.79586</v>
       </c>
       <c r="I267" t="n">
-        <v>0.14784</v>
+        <v>0.15094</v>
       </c>
       <c r="J267" t="n">
-        <v>0.5878599999999999</v>
+        <v>0.5847800000000002</v>
       </c>
     </row>
     <row r="268">
@@ -11130,22 +11130,22 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>0.8953599999999999</v>
+        <v>0.8988000000000002</v>
       </c>
       <c r="F268" t="n">
-        <v>0.9113</v>
+        <v>0.9138399999999999</v>
       </c>
       <c r="G268" t="n">
-        <v>0.90464</v>
+        <v>0.90974</v>
       </c>
       <c r="H268" t="n">
         <v>0.9846</v>
       </c>
       <c r="I268" t="n">
-        <v>0.14784</v>
+        <v>0.15094</v>
       </c>
       <c r="J268" t="n">
-        <v>0.5878599999999999</v>
+        <v>0.5847800000000002</v>
       </c>
     </row>
     <row r="269">
@@ -11170,22 +11170,22 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>0.2178</v>
+        <v>0.22122</v>
       </c>
       <c r="F269" t="n">
-        <v>0.21436</v>
+        <v>0.2169</v>
       </c>
       <c r="G269" t="n">
-        <v>0.3907599999999999</v>
+        <v>0.3959</v>
       </c>
       <c r="H269" t="n">
         <v>0.72204</v>
       </c>
       <c r="I269" t="n">
-        <v>0.15604</v>
+        <v>0.1577</v>
       </c>
       <c r="J269" t="n">
-        <v>0.5338399999999999</v>
+        <v>0.5322</v>
       </c>
     </row>
     <row r="270">
@@ -11210,22 +11210,22 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>0.37384</v>
+        <v>0.37892</v>
       </c>
       <c r="F270" t="n">
-        <v>0.40052</v>
+        <v>0.4041600000000001</v>
       </c>
       <c r="G270" t="n">
-        <v>0.53298</v>
+        <v>0.5399200000000001</v>
       </c>
       <c r="H270" t="n">
-        <v>0.82406</v>
+        <v>0.8258999999999999</v>
       </c>
       <c r="I270" t="n">
-        <v>0.15604</v>
+        <v>0.1577</v>
       </c>
       <c r="J270" t="n">
-        <v>0.5338399999999999</v>
+        <v>0.5322</v>
       </c>
     </row>
     <row r="271">
@@ -11250,22 +11250,22 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>0.9076799999999998</v>
+        <v>0.91112</v>
       </c>
       <c r="F271" t="n">
-        <v>0.91898</v>
+        <v>0.9215199999999999</v>
       </c>
       <c r="G271" t="n">
         <v>0.9384599999999998</v>
       </c>
       <c r="H271" t="n">
-        <v>0.9815400000000001</v>
+        <v>0.9866400000000001</v>
       </c>
       <c r="I271" t="n">
-        <v>0.15604</v>
+        <v>0.1577</v>
       </c>
       <c r="J271" t="n">
-        <v>0.5338399999999999</v>
+        <v>0.5322</v>
       </c>
     </row>
     <row r="272">
@@ -11281,7 +11281,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}</t>
+          <t>{"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -11290,22 +11290,22 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>0.24854</v>
+        <v>0.24582</v>
       </c>
       <c r="F272" t="n">
-        <v>0.25694</v>
+        <v>0.2492199999999999</v>
       </c>
       <c r="G272" t="n">
-        <v>0.39794</v>
+        <v>0.40102</v>
       </c>
       <c r="H272" t="n">
-        <v>0.72304</v>
+        <v>0.71692</v>
       </c>
       <c r="I272" t="n">
-        <v>0.12466</v>
+        <v>0.12694</v>
       </c>
       <c r="J272" t="n">
-        <v>0.5132800000000001</v>
+        <v>0.53424</v>
       </c>
     </row>
     <row r="273">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}</t>
+          <t>{"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -11330,22 +11330,22 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>0.3732</v>
+        <v>0.37276</v>
       </c>
       <c r="F273" t="n">
-        <v>0.40426</v>
+        <v>0.4026400000000001</v>
       </c>
       <c r="G273" t="n">
-        <v>0.50368</v>
+        <v>0.5046799999999999</v>
       </c>
       <c r="H273" t="n">
-        <v>0.81676</v>
+        <v>0.8186600000000001</v>
       </c>
       <c r="I273" t="n">
-        <v>0.12466</v>
+        <v>0.12694</v>
       </c>
       <c r="J273" t="n">
-        <v>0.5132800000000001</v>
+        <v>0.53424</v>
       </c>
     </row>
     <row r="274">
@@ -11361,7 +11361,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}</t>
+          <t>{"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -11370,22 +11370,22 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>0.88648</v>
+        <v>0.907</v>
       </c>
       <c r="F274" t="n">
-        <v>0.9030799999999999</v>
+        <v>0.9184599999999999</v>
       </c>
       <c r="G274" t="n">
-        <v>0.90768</v>
+        <v>0.9333400000000001</v>
       </c>
       <c r="H274" t="n">
-        <v>0.9815400000000001</v>
+        <v>0.9866400000000001</v>
       </c>
       <c r="I274" t="n">
-        <v>0.12466</v>
+        <v>0.12694</v>
       </c>
       <c r="J274" t="n">
-        <v>0.5132800000000001</v>
+        <v>0.53424</v>
       </c>
     </row>
     <row r="275">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}}</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -11410,22 +11410,22 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>0.1706</v>
+        <v>0.16992</v>
       </c>
       <c r="F275" t="n">
-        <v>0.15588</v>
+        <v>0.15538</v>
       </c>
       <c r="G275" t="n">
-        <v>0.3907600000000001</v>
+        <v>0.38974</v>
       </c>
       <c r="H275" t="n">
         <v>0.70052</v>
       </c>
       <c r="I275" t="n">
-        <v>0.16208</v>
+        <v>0.16968</v>
       </c>
       <c r="J275" t="n">
-        <v>0.5804600000000001</v>
+        <v>0.5803999999999999</v>
       </c>
     </row>
     <row r="276">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}}</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -11450,22 +11450,22 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>0.33268</v>
+        <v>0.3396</v>
       </c>
       <c r="F276" t="n">
-        <v>0.3502999999999999</v>
+        <v>0.35702</v>
       </c>
       <c r="G276" t="n">
-        <v>0.5204599999999999</v>
+        <v>0.5264800000000001</v>
       </c>
       <c r="H276" t="n">
-        <v>0.81254</v>
+        <v>0.8145200000000001</v>
       </c>
       <c r="I276" t="n">
-        <v>0.16208</v>
+        <v>0.16968</v>
       </c>
       <c r="J276" t="n">
-        <v>0.5804600000000001</v>
+        <v>0.5803999999999999</v>
       </c>
     </row>
     <row r="277">
@@ -11481,7 +11481,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}}</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -11490,22 +11490,22 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>0.9131400000000001</v>
+        <v>0.9199999999999999</v>
       </c>
       <c r="F277" t="n">
-        <v>0.9271600000000001</v>
+        <v>0.9323</v>
       </c>
       <c r="G277" t="n">
-        <v>0.94564</v>
+        <v>0.95074</v>
       </c>
       <c r="H277" t="n">
-        <v>0.9897</v>
+        <v>0.9949</v>
       </c>
       <c r="I277" t="n">
-        <v>0.16208</v>
+        <v>0.16968</v>
       </c>
       <c r="J277" t="n">
-        <v>0.5804600000000001</v>
+        <v>0.5803999999999999</v>
       </c>
     </row>
     <row r="278">
@@ -11542,10 +11542,10 @@
         <v>0.83178</v>
       </c>
       <c r="I278" t="n">
-        <v>0.1824399999999999</v>
+        <v>0.18462</v>
       </c>
       <c r="J278" t="n">
-        <v>0.34132</v>
+        <v>0.3391399999999999</v>
       </c>
     </row>
     <row r="279">
@@ -11570,22 +11570,22 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>0.5902799999999999</v>
+        <v>0.59246</v>
       </c>
       <c r="F279" t="n">
-        <v>0.6189199999999999</v>
+        <v>0.62336</v>
       </c>
       <c r="G279" t="n">
-        <v>0.68796</v>
+        <v>0.70056</v>
       </c>
       <c r="H279" t="n">
-        <v>0.9131</v>
+        <v>0.914</v>
       </c>
       <c r="I279" t="n">
-        <v>0.1824399999999999</v>
+        <v>0.18462</v>
       </c>
       <c r="J279" t="n">
-        <v>0.34132</v>
+        <v>0.3391399999999999</v>
       </c>
     </row>
     <row r="280">
@@ -11622,10 +11622,10 @@
         <v>0.9846</v>
       </c>
       <c r="I280" t="n">
-        <v>0.1824399999999999</v>
+        <v>0.18462</v>
       </c>
       <c r="J280" t="n">
-        <v>0.34132</v>
+        <v>0.3391399999999999</v>
       </c>
     </row>
     <row r="281">
@@ -11662,10 +11662,10 @@
         <v>0.79694</v>
       </c>
       <c r="I281" t="n">
-        <v>0.02107999999999999</v>
+        <v>0.02532000000000001</v>
       </c>
       <c r="J281" t="n">
-        <v>0.5396000000000001</v>
+        <v>0.5353600000000001</v>
       </c>
     </row>
     <row r="282">
@@ -11690,22 +11690,22 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>0.39542</v>
+        <v>0.39966</v>
       </c>
       <c r="F282" t="n">
-        <v>0.42454</v>
+        <v>0.43108</v>
       </c>
       <c r="G282" t="n">
-        <v>0.57058</v>
+        <v>0.58446</v>
       </c>
       <c r="H282" t="n">
-        <v>0.8313600000000001</v>
+        <v>0.8331200000000001</v>
       </c>
       <c r="I282" t="n">
-        <v>0.02107999999999999</v>
+        <v>0.02532000000000001</v>
       </c>
       <c r="J282" t="n">
-        <v>0.5396000000000001</v>
+        <v>0.5353600000000001</v>
       </c>
     </row>
     <row r="283">
@@ -11742,10 +11742,10 @@
         <v>0.9846</v>
       </c>
       <c r="I283" t="n">
-        <v>0.02107999999999999</v>
+        <v>0.02532000000000001</v>
       </c>
       <c r="J283" t="n">
-        <v>0.5396000000000001</v>
+        <v>0.5353600000000001</v>
       </c>
     </row>
     <row r="284">
@@ -11782,10 +11782,10 @@
         <v>0.7097199999999999</v>
       </c>
       <c r="I284" t="n">
-        <v>0.09029999999999999</v>
+        <v>0.08611999999999997</v>
       </c>
       <c r="J284" t="n">
-        <v>0.6508600000000001</v>
+        <v>0.6448</v>
       </c>
     </row>
     <row r="285">
@@ -11810,22 +11810,22 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>0.26844</v>
+        <v>0.26426</v>
       </c>
       <c r="F285" t="n">
-        <v>0.29162</v>
+        <v>0.29122</v>
       </c>
       <c r="G285" t="n">
-        <v>0.46388</v>
+        <v>0.46426</v>
       </c>
       <c r="H285" t="n">
-        <v>0.7894599999999999</v>
+        <v>0.78962</v>
       </c>
       <c r="I285" t="n">
-        <v>0.09029999999999999</v>
+        <v>0.08611999999999997</v>
       </c>
       <c r="J285" t="n">
-        <v>0.6508600000000001</v>
+        <v>0.6448</v>
       </c>
     </row>
     <row r="286">
@@ -11850,22 +11850,22 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>0.9193000000000001</v>
+        <v>0.90906</v>
       </c>
       <c r="F286" t="n">
-        <v>0.9395</v>
+        <v>0.9318</v>
       </c>
       <c r="G286" t="n">
-        <v>0.92616</v>
+        <v>0.91586</v>
       </c>
       <c r="H286" t="n">
         <v>1</v>
       </c>
       <c r="I286" t="n">
-        <v>0.09029999999999999</v>
+        <v>0.08611999999999997</v>
       </c>
       <c r="J286" t="n">
-        <v>0.6508600000000001</v>
+        <v>0.6448</v>
       </c>
     </row>
     <row r="287">
@@ -11890,22 +11890,22 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>0.16652</v>
+        <v>0.16992</v>
       </c>
       <c r="F287" t="n">
-        <v>0.15282</v>
+        <v>0.1554</v>
       </c>
       <c r="G287" t="n">
-        <v>0.38462</v>
+        <v>0.38976</v>
       </c>
       <c r="H287" t="n">
         <v>0.70052</v>
       </c>
       <c r="I287" t="n">
-        <v>0.16684</v>
+        <v>0.1662200000000001</v>
       </c>
       <c r="J287" t="n">
-        <v>0.5797800000000001</v>
+        <v>0.5804</v>
       </c>
     </row>
     <row r="288">
@@ -11930,22 +11930,22 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>0.33336</v>
+        <v>0.33614</v>
       </c>
       <c r="F288" t="n">
-        <v>0.35132</v>
+        <v>0.3544599999999999</v>
       </c>
       <c r="G288" t="n">
-        <v>0.5215</v>
+        <v>0.5213000000000001</v>
       </c>
       <c r="H288" t="n">
-        <v>0.81254</v>
+        <v>0.8145200000000001</v>
       </c>
       <c r="I288" t="n">
-        <v>0.16684</v>
+        <v>0.1662200000000001</v>
       </c>
       <c r="J288" t="n">
-        <v>0.5797800000000001</v>
+        <v>0.5804</v>
       </c>
     </row>
     <row r="289">
@@ -11970,22 +11970,22 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>0.9131400000000001</v>
+        <v>0.91654</v>
       </c>
       <c r="F289" t="n">
-        <v>0.9271600000000001</v>
+        <v>0.9297599999999999</v>
       </c>
       <c r="G289" t="n">
         <v>0.94564</v>
       </c>
       <c r="H289" t="n">
-        <v>0.9897</v>
+        <v>0.9949</v>
       </c>
       <c r="I289" t="n">
-        <v>0.16684</v>
+        <v>0.1662200000000001</v>
       </c>
       <c r="J289" t="n">
-        <v>0.5797800000000001</v>
+        <v>0.5804</v>
       </c>
     </row>
   </sheetData>

--- a/paper/sensitivity_analysis_all.xlsx
+++ b/paper/sensitivity_analysis_all.xlsx
@@ -3121,7 +3121,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.248, "environmental": 0.244, "comfort": 0.203, "practicality": 0.305}}</t>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.251251, "environmental": 0.245245, "comfort": 0.203203, "practicality": 0.3003}}</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3130,22 +3130,22 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.11316</v>
+        <v>0.10632</v>
       </c>
       <c r="F68" t="n">
-        <v>0.11998</v>
+        <v>0.11384</v>
       </c>
       <c r="G68" t="n">
-        <v>0.39076</v>
+        <v>0.38256</v>
       </c>
       <c r="H68" t="n">
-        <v>0.70974</v>
+        <v>0.7056600000000001</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1142</v>
+        <v>0.12104</v>
       </c>
       <c r="J68" t="n">
-        <v>0.6468400000000001</v>
+        <v>0.6445200000000002</v>
       </c>
     </row>
     <row r="69">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.248, "environmental": 0.244, "comfort": 0.203, "practicality": 0.305}}</t>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.251251, "environmental": 0.245245, "comfort": 0.203203, "practicality": 0.3003}}</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3173,19 +3173,19 @@
         <v>0.22736</v>
       </c>
       <c r="F69" t="n">
-        <v>0.24254</v>
+        <v>0.24204</v>
       </c>
       <c r="G69" t="n">
-        <v>0.4615600000000001</v>
+        <v>0.46462</v>
       </c>
       <c r="H69" t="n">
-        <v>0.7507600000000001</v>
+        <v>0.74664</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1142</v>
+        <v>0.12104</v>
       </c>
       <c r="J69" t="n">
-        <v>0.6468400000000001</v>
+        <v>0.6445200000000002</v>
       </c>
     </row>
     <row r="70">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.248, "environmental": 0.244, "comfort": 0.203, "practicality": 0.305}}</t>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.251251, "environmental": 0.245245, "comfort": 0.203203, "practicality": 0.3003}}</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3210,22 +3210,22 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.8742000000000001</v>
+        <v>0.8718800000000002</v>
       </c>
       <c r="F70" t="n">
-        <v>0.89688</v>
+        <v>0.8951399999999999</v>
       </c>
       <c r="G70" t="n">
-        <v>0.90564</v>
+        <v>0.9021399999999999</v>
       </c>
       <c r="H70" t="n">
         <v>0.9836599999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1142</v>
+        <v>0.12104</v>
       </c>
       <c r="J70" t="n">
-        <v>0.6468400000000001</v>
+        <v>0.6445200000000002</v>
       </c>
     </row>
     <row r="71">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.333666, "environmental": 0.313686, "comfort": 0.126873, "practicality": 0.225774}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.335, "environmental": 0.316, "comfort": 0.122, "practicality": 0.227}}</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3253,19 +3253,19 @@
         <v>0.04274</v>
       </c>
       <c r="F71" t="n">
-        <v>0.04049999999999999</v>
+        <v>0.03948</v>
       </c>
       <c r="G71" t="n">
-        <v>0.34668</v>
+        <v>0.3477</v>
       </c>
       <c r="H71" t="n">
-        <v>0.679</v>
+        <v>0.6769400000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>0.23726</v>
+        <v>0.2393</v>
       </c>
       <c r="J71" t="n">
-        <v>0.605</v>
+        <v>0.60608</v>
       </c>
     </row>
     <row r="72">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.333666, "environmental": 0.313686, "comfort": 0.126873, "practicality": 0.225774}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.335, "environmental": 0.316, "comfort": 0.122, "practicality": 0.227}}</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3290,22 +3290,22 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.28</v>
+        <v>0.28204</v>
       </c>
       <c r="F72" t="n">
-        <v>0.28974</v>
+        <v>0.29128</v>
       </c>
       <c r="G72" t="n">
-        <v>0.49332</v>
+        <v>0.4964200000000001</v>
       </c>
       <c r="H72" t="n">
         <v>0.77128</v>
       </c>
       <c r="I72" t="n">
-        <v>0.23726</v>
+        <v>0.2393</v>
       </c>
       <c r="J72" t="n">
-        <v>0.605</v>
+        <v>0.60608</v>
       </c>
     </row>
     <row r="73">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.333666, "environmental": 0.313686, "comfort": 0.126873, "practicality": 0.225774}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.335, "environmental": 0.316, "comfort": 0.122, "practicality": 0.227}}</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3330,22 +3330,22 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.885</v>
+        <v>0.88812</v>
       </c>
       <c r="F73" t="n">
-        <v>0.9026799999999999</v>
+        <v>0.90388</v>
       </c>
       <c r="G73" t="n">
-        <v>0.92432</v>
+        <v>0.9313</v>
       </c>
       <c r="H73" t="n">
-        <v>0.9929600000000001</v>
+        <v>0.9906599999999999</v>
       </c>
       <c r="I73" t="n">
-        <v>0.23726</v>
+        <v>0.2393</v>
       </c>
       <c r="J73" t="n">
-        <v>0.605</v>
+        <v>0.60608</v>
       </c>
     </row>
     <row r="74">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.248, "environmental": 0.244, "comfort": 0.203, "practicality": 0.305}}</t>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.251251, "environmental": 0.245245, "comfort": 0.203203, "practicality": 0.3003}}</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6010,22 +6010,22 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>-0.01604</v>
+        <v>-0.0147</v>
       </c>
       <c r="F140" t="n">
-        <v>-0.021</v>
+        <v>-0.01948</v>
       </c>
       <c r="G140" t="n">
-        <v>0.2981</v>
+        <v>0.30012</v>
       </c>
       <c r="H140" t="n">
-        <v>0.65778</v>
+        <v>0.65878</v>
       </c>
       <c r="I140" t="n">
-        <v>0.18734</v>
+        <v>0.1928</v>
       </c>
       <c r="J140" t="n">
-        <v>0.68554</v>
+        <v>0.6780400000000001</v>
       </c>
     </row>
     <row r="141">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.248, "environmental": 0.244, "comfort": 0.203, "practicality": 0.305}}</t>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.251251, "environmental": 0.245245, "comfort": 0.203203, "practicality": 0.3003}}</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6050,22 +6050,22 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.1713</v>
+        <v>0.1781</v>
       </c>
       <c r="F141" t="n">
-        <v>0.18616</v>
+        <v>0.19178</v>
       </c>
       <c r="G141" t="n">
-        <v>0.45026</v>
+        <v>0.45436</v>
       </c>
       <c r="H141" t="n">
-        <v>0.7712600000000001</v>
+        <v>0.77744</v>
       </c>
       <c r="I141" t="n">
-        <v>0.18734</v>
+        <v>0.1928</v>
       </c>
       <c r="J141" t="n">
-        <v>0.68554</v>
+        <v>0.6780400000000001</v>
       </c>
     </row>
     <row r="142">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.248, "environmental": 0.244, "comfort": 0.203, "practicality": 0.305}}</t>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.251251, "environmental": 0.245245, "comfort": 0.203203, "practicality": 0.3003}}</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -6090,22 +6090,22 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.85684</v>
+        <v>0.8561400000000001</v>
       </c>
       <c r="F142" t="n">
-        <v>0.87102</v>
+        <v>0.8731</v>
       </c>
       <c r="G142" t="n">
-        <v>0.86126</v>
+        <v>0.85512</v>
       </c>
       <c r="H142" t="n">
-        <v>0.97226</v>
+        <v>0.9773999999999999</v>
       </c>
       <c r="I142" t="n">
-        <v>0.18734</v>
+        <v>0.1928</v>
       </c>
       <c r="J142" t="n">
-        <v>0.68554</v>
+        <v>0.6780400000000001</v>
       </c>
     </row>
     <row r="143">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.333666, "environmental": 0.313686, "comfort": 0.126873, "practicality": 0.225774}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.335, "environmental": 0.316, "comfort": 0.122, "practicality": 0.227}}</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -6130,22 +6130,22 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>-0.007179999999999997</v>
+        <v>-0.006460000000000002</v>
       </c>
       <c r="F143" t="n">
         <v>-0.01796</v>
       </c>
       <c r="G143" t="n">
-        <v>0.30116</v>
+        <v>0.30324</v>
       </c>
       <c r="H143" t="n">
-        <v>0.68136</v>
+        <v>0.6793199999999999</v>
       </c>
       <c r="I143" t="n">
-        <v>0.22564</v>
+        <v>0.2263</v>
       </c>
       <c r="J143" t="n">
-        <v>0.66712</v>
+        <v>0.66916</v>
       </c>
     </row>
     <row r="144">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.333666, "environmental": 0.313686, "comfort": 0.126873, "practicality": 0.225774}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.335, "environmental": 0.316, "comfort": 0.122, "practicality": 0.227}}</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -6170,22 +6170,22 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.21846</v>
+        <v>0.21984</v>
       </c>
       <c r="F144" t="n">
-        <v>0.23538</v>
+        <v>0.23642</v>
       </c>
       <c r="G144" t="n">
-        <v>0.4605399999999999</v>
+        <v>0.46258</v>
       </c>
       <c r="H144" t="n">
-        <v>0.7846200000000001</v>
+        <v>0.78462</v>
       </c>
       <c r="I144" t="n">
-        <v>0.22564</v>
+        <v>0.2263</v>
       </c>
       <c r="J144" t="n">
-        <v>0.66712</v>
+        <v>0.66916</v>
       </c>
     </row>
     <row r="145">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.333666, "environmental": 0.313686, "comfort": 0.126873, "practicality": 0.225774}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.335, "environmental": 0.316, "comfort": 0.122, "practicality": 0.227}}</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -6210,22 +6210,22 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0.88558</v>
+        <v>0.889</v>
       </c>
       <c r="F145" t="n">
-        <v>0.89984</v>
+        <v>0.90234</v>
       </c>
       <c r="G145" t="n">
-        <v>0.9270400000000001</v>
+        <v>0.93216</v>
       </c>
       <c r="H145" t="n">
         <v>0.98356</v>
       </c>
       <c r="I145" t="n">
-        <v>0.22564</v>
+        <v>0.2263</v>
       </c>
       <c r="J145" t="n">
-        <v>0.66712</v>
+        <v>0.66916</v>
       </c>
     </row>
     <row r="146">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.248, "environmental": 0.244, "comfort": 0.203, "practicality": 0.305}}</t>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.251251, "environmental": 0.245245, "comfort": 0.203203, "practicality": 0.3003}}</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -8890,22 +8890,22 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>0.09372</v>
+        <v>0.09301999999999999</v>
       </c>
       <c r="F212" t="n">
-        <v>0.09409999999999999</v>
+        <v>0.09408000000000001</v>
       </c>
       <c r="G212" t="n">
-        <v>0.3369</v>
+        <v>0.3338</v>
       </c>
       <c r="H212" t="n">
-        <v>0.6932</v>
+        <v>0.6953</v>
       </c>
       <c r="I212" t="n">
-        <v>0.14664</v>
+        <v>0.14254</v>
       </c>
       <c r="J212" t="n">
-        <v>0.65218</v>
+        <v>0.65834</v>
       </c>
     </row>
     <row r="213">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.248, "environmental": 0.244, "comfort": 0.203, "practicality": 0.305}}</t>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.251251, "environmental": 0.245245, "comfort": 0.203203, "practicality": 0.3003}}</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -8930,22 +8930,22 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>0.24036</v>
+        <v>0.23556</v>
       </c>
       <c r="F213" t="n">
-        <v>0.26206</v>
+        <v>0.25692</v>
       </c>
       <c r="G213" t="n">
-        <v>0.49026</v>
+        <v>0.4800000000000001</v>
       </c>
       <c r="H213" t="n">
-        <v>0.78976</v>
+        <v>0.78872</v>
       </c>
       <c r="I213" t="n">
-        <v>0.14664</v>
+        <v>0.14254</v>
       </c>
       <c r="J213" t="n">
-        <v>0.65218</v>
+        <v>0.65834</v>
       </c>
     </row>
     <row r="214">
@@ -8961,7 +8961,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.248, "environmental": 0.244, "comfort": 0.203, "practicality": 0.305}}</t>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.251251, "environmental": 0.245245, "comfort": 0.203203, "practicality": 0.3003}}</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -8970,22 +8970,22 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>0.89254</v>
+        <v>0.8939</v>
       </c>
       <c r="F214" t="n">
-        <v>0.9111799999999999</v>
+        <v>0.9117</v>
       </c>
       <c r="G214" t="n">
-        <v>0.9096399999999999</v>
+        <v>0.9116799999999999</v>
       </c>
       <c r="H214" t="n">
         <v>0.9887</v>
       </c>
       <c r="I214" t="n">
-        <v>0.14664</v>
+        <v>0.14254</v>
       </c>
       <c r="J214" t="n">
-        <v>0.65218</v>
+        <v>0.65834</v>
       </c>
     </row>
     <row r="215">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.333666, "environmental": 0.313686, "comfort": 0.126873, "practicality": 0.225774}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.335, "environmental": 0.316, "comfort": 0.122, "practicality": 0.227}}</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -9010,22 +9010,22 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>0.08821999999999999</v>
+        <v>0.09029999999999999</v>
       </c>
       <c r="F215" t="n">
-        <v>0.08734</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="G215" t="n">
-        <v>0.342</v>
+        <v>0.34612</v>
       </c>
       <c r="H215" t="n">
-        <v>0.70766</v>
+        <v>0.70662</v>
       </c>
       <c r="I215" t="n">
-        <v>0.25878</v>
+        <v>0.2594400000000001</v>
       </c>
       <c r="J215" t="n">
-        <v>0.5489400000000001</v>
+        <v>0.5517</v>
       </c>
     </row>
     <row r="216">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.333666, "environmental": 0.313686, "comfort": 0.126873, "practicality": 0.225774}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.335, "environmental": 0.316, "comfort": 0.122, "practicality": 0.227}}</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -9050,22 +9050,22 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>0.347</v>
+        <v>0.3497400000000001</v>
       </c>
       <c r="F216" t="n">
-        <v>0.36874</v>
+        <v>0.3718</v>
       </c>
       <c r="G216" t="n">
-        <v>0.5599999999999999</v>
+        <v>0.56206</v>
       </c>
       <c r="H216" t="n">
-        <v>0.8297399999999999</v>
+        <v>0.8328199999999999</v>
       </c>
       <c r="I216" t="n">
-        <v>0.25878</v>
+        <v>0.2594400000000001</v>
       </c>
       <c r="J216" t="n">
-        <v>0.5489400000000001</v>
+        <v>0.5517</v>
       </c>
     </row>
     <row r="217">
@@ -9081,7 +9081,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.333666, "environmental": 0.313686, "comfort": 0.126873, "practicality": 0.225774}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.335, "environmental": 0.316, "comfort": 0.122, "practicality": 0.227}}</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -9090,22 +9090,22 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>0.8959400000000001</v>
+        <v>0.90144</v>
       </c>
       <c r="F217" t="n">
-        <v>0.9106799999999999</v>
+        <v>0.91476</v>
       </c>
       <c r="G217" t="n">
-        <v>0.924</v>
+        <v>0.9322199999999998</v>
       </c>
       <c r="H217" t="n">
         <v>0.98766</v>
       </c>
       <c r="I217" t="n">
-        <v>0.25878</v>
+        <v>0.2594400000000001</v>
       </c>
       <c r="J217" t="n">
-        <v>0.5489400000000001</v>
+        <v>0.5517</v>
       </c>
     </row>
     <row r="218">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.248, "environmental": 0.244, "comfort": 0.203, "practicality": 0.305}}</t>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.251251, "environmental": 0.245245, "comfort": 0.203203, "practicality": 0.3003}}</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -11770,22 +11770,22 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>0.17814</v>
+        <v>0.17196</v>
       </c>
       <c r="F284" t="n">
-        <v>0.18052</v>
+        <v>0.1754</v>
       </c>
       <c r="G284" t="n">
-        <v>0.36822</v>
+        <v>0.35794</v>
       </c>
       <c r="H284" t="n">
-        <v>0.7097199999999999</v>
+        <v>0.7087</v>
       </c>
       <c r="I284" t="n">
-        <v>0.08611999999999997</v>
+        <v>0.08056000000000005</v>
       </c>
       <c r="J284" t="n">
-        <v>0.6448</v>
+        <v>0.6565399999999999</v>
       </c>
     </row>
     <row r="285">
@@ -11801,7 +11801,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.248, "environmental": 0.244, "comfort": 0.203, "practicality": 0.305}}</t>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.251251, "environmental": 0.245245, "comfort": 0.203203, "practicality": 0.3003}}</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -11810,22 +11810,22 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>0.26426</v>
+        <v>0.25252</v>
       </c>
       <c r="F285" t="n">
-        <v>0.29122</v>
+        <v>0.27618</v>
       </c>
       <c r="G285" t="n">
-        <v>0.46426</v>
+        <v>0.44974</v>
       </c>
       <c r="H285" t="n">
-        <v>0.78962</v>
+        <v>0.7823800000000001</v>
       </c>
       <c r="I285" t="n">
-        <v>0.08611999999999997</v>
+        <v>0.08056000000000005</v>
       </c>
       <c r="J285" t="n">
-        <v>0.6448</v>
+        <v>0.6565399999999999</v>
       </c>
     </row>
     <row r="286">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.248, "environmental": 0.244, "comfort": 0.203, "practicality": 0.305}}</t>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.251251, "environmental": 0.245245, "comfort": 0.203203, "practicality": 0.3003}}</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -11862,10 +11862,10 @@
         <v>1</v>
       </c>
       <c r="I286" t="n">
-        <v>0.08611999999999997</v>
+        <v>0.08056000000000005</v>
       </c>
       <c r="J286" t="n">
-        <v>0.6448</v>
+        <v>0.6565399999999999</v>
       </c>
     </row>
     <row r="287">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.333666, "environmental": 0.313686, "comfort": 0.126873, "practicality": 0.225774}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.335, "environmental": 0.316, "comfort": 0.122, "practicality": 0.227}}</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -11893,19 +11893,19 @@
         <v>0.16992</v>
       </c>
       <c r="F287" t="n">
-        <v>0.1554</v>
+        <v>0.15538</v>
       </c>
       <c r="G287" t="n">
-        <v>0.38976</v>
+        <v>0.38974</v>
       </c>
       <c r="H287" t="n">
         <v>0.70052</v>
       </c>
       <c r="I287" t="n">
-        <v>0.1662200000000001</v>
+        <v>0.16968</v>
       </c>
       <c r="J287" t="n">
-        <v>0.5804</v>
+        <v>0.5803999999999999</v>
       </c>
     </row>
     <row r="288">
@@ -11921,7 +11921,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.333666, "environmental": 0.313686, "comfort": 0.126873, "practicality": 0.225774}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.335, "environmental": 0.316, "comfort": 0.122, "practicality": 0.227}}</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -11930,22 +11930,22 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>0.33614</v>
+        <v>0.3396</v>
       </c>
       <c r="F288" t="n">
-        <v>0.3544599999999999</v>
+        <v>0.35702</v>
       </c>
       <c r="G288" t="n">
-        <v>0.5213000000000001</v>
+        <v>0.5264800000000001</v>
       </c>
       <c r="H288" t="n">
         <v>0.8145200000000001</v>
       </c>
       <c r="I288" t="n">
-        <v>0.1662200000000001</v>
+        <v>0.16968</v>
       </c>
       <c r="J288" t="n">
-        <v>0.5804</v>
+        <v>0.5803999999999999</v>
       </c>
     </row>
     <row r="289">
@@ -11961,7 +11961,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.333666, "environmental": 0.313686, "comfort": 0.126873, "practicality": 0.225774}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.335, "environmental": 0.316, "comfort": 0.122, "practicality": 0.227}}</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -11970,22 +11970,22 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>0.91654</v>
+        <v>0.9199999999999999</v>
       </c>
       <c r="F289" t="n">
-        <v>0.9297599999999999</v>
+        <v>0.9323</v>
       </c>
       <c r="G289" t="n">
-        <v>0.94564</v>
+        <v>0.95074</v>
       </c>
       <c r="H289" t="n">
         <v>0.9949</v>
       </c>
       <c r="I289" t="n">
-        <v>0.1662200000000001</v>
+        <v>0.16968</v>
       </c>
       <c r="J289" t="n">
-        <v>0.5804</v>
+        <v>0.5803999999999999</v>
       </c>
     </row>
   </sheetData>
